--- a/Plantilla-modelo.xlsx
+++ b/Plantilla-modelo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollo-software\reporte-obras-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6996F370-EE6A-4912-AE45-D140E5C84406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8C850D-6579-4502-9A74-026C682C149A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="947" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="947" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ANTEQUERA" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="396">
   <si>
     <t>REVISADO</t>
   </si>
@@ -1429,6 +1429,9 @@
   </si>
   <si>
     <t>4.1 Esta tarea es una prueba para ver si funciona el script</t>
+  </si>
+  <si>
+    <t>1.7 Esta tarea es una prueba para ver si funciona el script</t>
   </si>
 </sst>
 </file>
@@ -1643,15 +1646,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1670,6 +1664,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1678,12 +1684,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1693,14 +1693,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1728,6 +1722,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -2107,13 +2110,13 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -2143,13 +2146,13 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -2185,25 +2188,25 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="35"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="32"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
@@ -2279,25 +2282,25 @@
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="32"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="35"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="32"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
@@ -2439,13 +2442,13 @@
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="43" t="s">
+      <c r="D27" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="45"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
@@ -2517,25 +2520,25 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="D33" s="40" t="s">
+      <c r="D33" s="36" t="s">
         <v>169</v>
       </c>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="42"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="38"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="14"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="36" t="s">
+      <c r="D34" s="39" t="s">
         <v>323</v>
       </c>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="38"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="41"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
@@ -2595,13 +2598,13 @@
       <c r="A39" s="13"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="36" t="s">
+      <c r="D39" s="39" t="s">
         <v>322</v>
       </c>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="38"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="41"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
@@ -2667,13 +2670,13 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="30" t="s">
+      <c r="D44" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="32"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="29"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
@@ -2754,6 +2757,32 @@
     <row r="282" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D16:H16"/>
@@ -2770,32 +2799,6 @@
     <mergeCell ref="D26:H26"/>
     <mergeCell ref="D27:H27"/>
     <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D43:H43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2847,49 +2850,49 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="27" t="s">
         <v>298</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="32"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="29"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="30" t="s">
         <v>299</v>
       </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="35"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="32"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="35"/>
     </row>
     <row r="7" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
@@ -3067,13 +3070,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="D8:H8"/>
@@ -3086,6 +3082,13 @@
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3128,13 +3131,13 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -3152,49 +3155,49 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="42"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="36" t="s">
         <v>207</v>
       </c>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="42"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="38"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -3230,49 +3233,49 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
     </row>
     <row r="14" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
@@ -3386,85 +3389,85 @@
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="36" t="s">
+      <c r="D22" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="38"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="12"/>
-      <c r="D23" s="36" t="s">
+      <c r="D23" s="39" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="38"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="36" t="s">
+      <c r="D24" s="39" t="s">
         <v>302</v>
       </c>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="38"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="41"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="12"/>
-      <c r="D25" s="36" t="s">
+      <c r="D25" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="38"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="41"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="12"/>
-      <c r="D26" s="36" t="s">
+      <c r="D26" s="39" t="s">
         <v>304</v>
       </c>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="38"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="41"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="12"/>
-      <c r="D27" s="36" t="s">
+      <c r="D27" s="39" t="s">
         <v>305</v>
       </c>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="38"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="12"/>
-      <c r="D28" s="36" t="s">
+      <c r="D28" s="39" t="s">
         <v>306</v>
       </c>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="38"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="41"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -3500,13 +3503,13 @@
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="36" t="s">
+      <c r="D31" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="E31" s="37"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="38"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="41"/>
     </row>
     <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
@@ -3674,13 +3677,13 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="40" t="s">
+      <c r="D44" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="42"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="38"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
@@ -3698,25 +3701,25 @@
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="40" t="s">
+      <c r="D46" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="42"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="38"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="40" t="s">
+      <c r="D47" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="42"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="38"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
@@ -3860,13 +3863,13 @@
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="43" t="s">
+      <c r="D58" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="E58" s="44"/>
-      <c r="F58" s="44"/>
-      <c r="G58" s="44"/>
-      <c r="H58" s="45"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="44"/>
     </row>
     <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2"/>
@@ -4154,61 +4157,61 @@
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
-      <c r="D81" s="30" t="s">
+      <c r="D81" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="E81" s="31"/>
-      <c r="F81" s="31"/>
-      <c r="G81" s="31"/>
-      <c r="H81" s="32"/>
+      <c r="E81" s="28"/>
+      <c r="F81" s="28"/>
+      <c r="G81" s="28"/>
+      <c r="H81" s="29"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
-      <c r="D82" s="33" t="s">
+      <c r="D82" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="E82" s="34"/>
-      <c r="F82" s="34"/>
-      <c r="G82" s="34"/>
-      <c r="H82" s="35"/>
+      <c r="E82" s="31"/>
+      <c r="F82" s="31"/>
+      <c r="G82" s="31"/>
+      <c r="H82" s="32"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
-      <c r="D83" s="27" t="s">
+      <c r="D83" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="E83" s="28"/>
-      <c r="F83" s="28"/>
-      <c r="G83" s="28"/>
-      <c r="H83" s="29"/>
+      <c r="E83" s="34"/>
+      <c r="F83" s="34"/>
+      <c r="G83" s="34"/>
+      <c r="H83" s="35"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
-      <c r="D84" s="27" t="s">
+      <c r="D84" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="E84" s="28"/>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
-      <c r="H84" s="29"/>
+      <c r="E84" s="34"/>
+      <c r="F84" s="34"/>
+      <c r="G84" s="34"/>
+      <c r="H84" s="35"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
-      <c r="D85" s="30" t="s">
+      <c r="D85" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="E85" s="31"/>
-      <c r="F85" s="31"/>
-      <c r="G85" s="31"/>
-      <c r="H85" s="32"/>
+      <c r="E85" s="28"/>
+      <c r="F85" s="28"/>
+      <c r="G85" s="28"/>
+      <c r="H85" s="29"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
@@ -4290,24 +4293,61 @@
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D87:H87"/>
+    <mergeCell ref="D88:H88"/>
+    <mergeCell ref="D89:H89"/>
+    <mergeCell ref="D74:H74"/>
+    <mergeCell ref="D63:H63"/>
+    <mergeCell ref="D64:H64"/>
+    <mergeCell ref="D65:H65"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D67:H67"/>
+    <mergeCell ref="D68:H68"/>
+    <mergeCell ref="D69:H69"/>
+    <mergeCell ref="D70:H70"/>
+    <mergeCell ref="D71:H71"/>
+    <mergeCell ref="D72:H72"/>
+    <mergeCell ref="D90:H90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="D86:H86"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="D76:H76"/>
+    <mergeCell ref="D77:H77"/>
+    <mergeCell ref="D78:H78"/>
+    <mergeCell ref="D79:H79"/>
+    <mergeCell ref="D80:H80"/>
+    <mergeCell ref="D81:H81"/>
+    <mergeCell ref="D82:H82"/>
+    <mergeCell ref="D83:H83"/>
+    <mergeCell ref="D84:H84"/>
+    <mergeCell ref="D85:H85"/>
+    <mergeCell ref="D73:H73"/>
+    <mergeCell ref="D62:H62"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D56:H56"/>
+    <mergeCell ref="D57:H57"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="D61:H61"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D49:H49"/>
     <mergeCell ref="D37:H37"/>
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="D21:H21"/>
@@ -4324,61 +4364,24 @@
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="D26:H26"/>
     <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D73:H73"/>
-    <mergeCell ref="D62:H62"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D56:H56"/>
-    <mergeCell ref="D57:H57"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="D61:H61"/>
-    <mergeCell ref="D90:H90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="D86:H86"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="D76:H76"/>
-    <mergeCell ref="D77:H77"/>
-    <mergeCell ref="D78:H78"/>
-    <mergeCell ref="D79:H79"/>
-    <mergeCell ref="D80:H80"/>
-    <mergeCell ref="D81:H81"/>
-    <mergeCell ref="D82:H82"/>
-    <mergeCell ref="D83:H83"/>
-    <mergeCell ref="D84:H84"/>
-    <mergeCell ref="D85:H85"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D87:H87"/>
-    <mergeCell ref="D88:H88"/>
-    <mergeCell ref="D89:H89"/>
-    <mergeCell ref="D74:H74"/>
-    <mergeCell ref="D63:H63"/>
-    <mergeCell ref="D64:H64"/>
-    <mergeCell ref="D65:H65"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D67:H67"/>
-    <mergeCell ref="D68:H68"/>
-    <mergeCell ref="D69:H69"/>
-    <mergeCell ref="D70:H70"/>
-    <mergeCell ref="D71:H71"/>
-    <mergeCell ref="D72:H72"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4420,13 +4423,13 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -4456,37 +4459,37 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="35"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -4522,49 +4525,49 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
     </row>
     <row r="14" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
@@ -4678,13 +4681,13 @@
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="43" t="s">
+      <c r="D22" s="42" t="s">
         <v>312</v>
       </c>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="45"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="44"/>
     </row>
     <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
@@ -4952,12 +4955,28 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
@@ -4970,28 +4989,12 @@
     <mergeCell ref="D17:H17"/>
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5036,49 +5039,49 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="27" t="s">
         <v>298</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="32"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="29"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="30" t="s">
         <v>299</v>
       </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="35"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="32"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="35"/>
     </row>
     <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
@@ -5256,6 +5259,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="D2:H2"/>
@@ -5268,13 +5278,6 @@
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5285,7 +5288,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A7:H60"/>
+  <dimension ref="A7:H61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -5316,13 +5319,13 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -5352,308 +5355,308 @@
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="29"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="35"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="42"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="38"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D15" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="26"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="23"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="32"/>
+      <c r="D16" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="23"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="35"/>
+      <c r="D17" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="27" t="s">
-        <v>379</v>
-      </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
+      <c r="D18" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="32"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="27" t="s">
-        <v>380</v>
-      </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="29"/>
-    </row>
-    <row r="20" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D19" s="33" t="s">
+        <v>379</v>
+      </c>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="35"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="35"/>
+    </row>
+    <row r="21" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="23"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="23"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D22" s="24" t="s">
         <v>324</v>
       </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="26"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="23"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="32"/>
+      <c r="D23" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="23"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="35"/>
+      <c r="D24" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="29"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="29"/>
+      <c r="D25" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="32"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="35"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="35"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D28" s="24" t="s">
         <v>325</v>
       </c>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="26"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="21" t="s">
-        <v>253</v>
-      </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="23"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="26"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
-      <c r="D29" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="32"/>
+      <c r="D29" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="23"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
-      <c r="D30" s="33" t="s">
-        <v>255</v>
-      </c>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="35"/>
+      <c r="D30" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="29"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="32"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="29"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="35"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="D33" s="24" t="s">
         <v>327</v>
       </c>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="26"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="23"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="26"/>
     </row>
     <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="21" t="s">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
@@ -5665,7 +5668,7 @@
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="21" t="s">
-        <v>329</v>
+        <v>261</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="22"/>
@@ -5677,7 +5680,7 @@
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
@@ -5689,277 +5692,277 @@
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="21" t="s">
-        <v>263</v>
+        <v>330</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="22"/>
       <c r="G37" s="22"/>
       <c r="H37" s="23"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="23"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D38" s="24" t="s">
+      <c r="D39" s="24" t="s">
         <v>331</v>
       </c>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="26"/>
-    </row>
-    <row r="39" spans="1:8" ht="78.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="43" t="s">
-        <v>332</v>
-      </c>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="44"/>
-      <c r="H39" s="45"/>
-    </row>
-    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="26"/>
+    </row>
+    <row r="40" spans="1:8" ht="78.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="21" t="s">
-        <v>333</v>
-      </c>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="23"/>
+      <c r="D40" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="44"/>
     </row>
     <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="21" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
       <c r="G41" s="22"/>
       <c r="H41" s="23"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="23"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D42" s="24" t="s">
+      <c r="D43" s="24" t="s">
         <v>335</v>
       </c>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="26"/>
-    </row>
-    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="21" t="s">
-        <v>319</v>
-      </c>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="23"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="26"/>
     </row>
     <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="21" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
       <c r="G44" s="22"/>
       <c r="H44" s="23"/>
     </row>
-    <row r="45" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="21" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="22"/>
       <c r="G45" s="22"/>
       <c r="H45" s="23"/>
     </row>
-    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="21" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
       <c r="G46" s="22"/>
       <c r="H46" s="23"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
+    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="23"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D47" s="24" t="s">
+      <c r="D48" s="24" t="s">
         <v>338</v>
       </c>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="26"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="36" t="s">
-        <v>339</v>
-      </c>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="38"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="26"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
-      <c r="D49" s="27" t="s">
-        <v>340</v>
-      </c>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="29"/>
+      <c r="D49" s="39" t="s">
+        <v>339</v>
+      </c>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="41"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="36" t="s">
-        <v>341</v>
-      </c>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="38"/>
-    </row>
-    <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D50" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="34"/>
+      <c r="H50" s="35"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="36" t="s">
+      <c r="D51" s="39" t="s">
+        <v>341</v>
+      </c>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="41"/>
+    </row>
+    <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="39" t="s">
         <v>342</v>
       </c>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="37"/>
-      <c r="H51" s="38"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="1" t="s">
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="41"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D52" s="24" t="s">
+      <c r="D53" s="24" t="s">
         <v>343</v>
       </c>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="26"/>
-    </row>
-    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="21" t="s">
-        <v>344</v>
-      </c>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="23"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="26"/>
     </row>
     <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="21" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="22"/>
       <c r="G54" s="22"/>
       <c r="H54" s="23"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
+    <row r="55" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="23"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D55" s="24" t="s">
+      <c r="D56" s="24" t="s">
         <v>346</v>
       </c>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="26"/>
-    </row>
-    <row r="56" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="21" t="s">
-        <v>347</v>
-      </c>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="23"/>
-    </row>
-    <row r="57" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="26"/>
+    </row>
+    <row r="57" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="21" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="22"/>
@@ -5971,7 +5974,7 @@
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="21" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E58" s="22"/>
       <c r="F58" s="22"/>
@@ -5983,7 +5986,7 @@
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="21" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E59" s="22"/>
       <c r="F59" s="22"/>
@@ -5995,27 +5998,62 @@
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="21" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
       <c r="G60" s="22"/>
       <c r="H60" s="23"/>
     </row>
+    <row r="61" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="23"/>
+    </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="D61:H61"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D56:H56"/>
+    <mergeCell ref="D57:H57"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
     <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D21:H21"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D34:H34"/>
     <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D36:H36"/>
     <mergeCell ref="D22:H22"/>
     <mergeCell ref="D23:H23"/>
     <mergeCell ref="D24:H24"/>
@@ -6026,36 +6064,13 @@
     <mergeCell ref="D29:H29"/>
     <mergeCell ref="D30:H30"/>
     <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D57:H57"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D56:H56"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6102,13 +6117,13 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -6126,49 +6141,49 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="42"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="42"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="38"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -6204,49 +6219,49 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
     </row>
     <row r="14" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
@@ -6348,13 +6363,13 @@
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="36" t="s">
+      <c r="D21" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="38"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="41"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -6532,6 +6547,27 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="D2:H2"/>
@@ -6544,27 +6580,6 @@
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="D11:H11"/>
     <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
   </mergeCells>
   <pageMargins left="0.70866141732283461" right="0.70866141732283461" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6576,7 +6591,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -6607,13 +6622,13 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -6643,164 +6658,164 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="33" t="s">
         <v>217</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="35"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D9" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="23"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
+      <c r="D10" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="23"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35"/>
+      <c r="D11" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="27" t="s">
-        <v>364</v>
-      </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
+      <c r="D12" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="32"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="27" t="s">
-        <v>365</v>
-      </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
-    </row>
-    <row r="14" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D13" s="33" t="s">
+        <v>364</v>
+      </c>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="35"/>
+    </row>
+    <row r="15" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="23"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="23"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D16" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="23"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="26"/>
     </row>
     <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
@@ -6812,7 +6827,7 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="21" t="s">
-        <v>361</v>
+        <v>241</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -6824,7 +6839,7 @@
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="21" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="22"/>
@@ -6836,265 +6851,265 @@
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="21" t="s">
-        <v>96</v>
+        <v>362</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>
       <c r="H20" s="23"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="23"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D22" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="26"/>
-    </row>
-    <row r="22" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="43" t="s">
-        <v>363</v>
-      </c>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="45"/>
-    </row>
-    <row r="23" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26"/>
+    </row>
+    <row r="23" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="23"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D23" s="42" t="s">
+        <v>363</v>
+      </c>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="44"/>
+    </row>
+    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="21" t="s">
-        <v>100</v>
+        <v>239</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
       <c r="H24" s="23"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="23"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D26" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="26"/>
-    </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="23"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="26"/>
+    </row>
+    <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
       <c r="G27" s="22"/>
       <c r="H27" s="23"/>
     </row>
-    <row r="28" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="21" t="s">
-        <v>352</v>
+        <v>103</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
       <c r="H28" s="23"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="23"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="24" t="s">
+      <c r="D30" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="26"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="38"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="26"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="29"/>
+      <c r="D31" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="41"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="38"/>
-    </row>
-    <row r="33" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D32" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="35"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="D33" s="36" t="s">
+      <c r="D33" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="41"/>
+    </row>
+    <row r="34" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="38"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="41"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D35" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="26"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="23"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="26"/>
     </row>
     <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
       <c r="G36" s="22"/>
       <c r="H36" s="23"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="23"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="24" t="s">
+      <c r="D38" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="26"/>
-    </row>
-    <row r="38" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="23"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="26"/>
+    </row>
+    <row r="39" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="21" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E39" s="22"/>
       <c r="F39" s="22"/>
@@ -7106,7 +7121,7 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="21" t="s">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
@@ -7118,7 +7133,7 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
@@ -7130,23 +7145,50 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
       <c r="G42" s="22"/>
       <c r="H42" s="23"/>
     </row>
+    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="23"/>
+    </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D21:H21"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="D11:H11"/>
     <mergeCell ref="D12:H12"/>
@@ -7157,28 +7199,13 @@
     <mergeCell ref="D17:H17"/>
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7221,13 +7248,13 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -7257,37 +7284,37 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="33" t="s">
         <v>219</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="33" t="s">
         <v>220</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="35"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -7323,49 +7350,49 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="33" t="s">
         <v>366</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="33" t="s">
         <v>367</v>
       </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
     </row>
     <row r="14" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
@@ -7479,61 +7506,61 @@
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="43" t="s">
+      <c r="D22" s="42" t="s">
         <v>370</v>
       </c>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="45"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="44"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="43" t="s">
+      <c r="D23" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="45"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="44"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="43" t="s">
+      <c r="D24" s="42" t="s">
         <v>222</v>
       </c>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="45"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="44"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="43" t="s">
+      <c r="D25" s="42" t="s">
         <v>223</v>
       </c>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="45"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="43" t="s">
+      <c r="D26" s="42" t="s">
         <v>224</v>
       </c>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="45"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="44"/>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
@@ -7635,49 +7662,49 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="36" t="s">
+      <c r="D34" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="38"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="41"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="27" t="s">
+      <c r="D35" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="29"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="35"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
-      <c r="D36" s="36" t="s">
+      <c r="D36" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="38"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="41"/>
     </row>
     <row r="37" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="36" t="s">
+      <c r="D37" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="38"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="41"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
@@ -7801,34 +7828,6 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
     <mergeCell ref="D35:H35"/>
     <mergeCell ref="D36:H36"/>
     <mergeCell ref="D21:H21"/>
@@ -7845,6 +7844,34 @@
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7887,13 +7914,13 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -7923,37 +7950,37 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="35"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -7989,49 +8016,49 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
     </row>
     <row r="14" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
@@ -8079,49 +8106,49 @@
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="30" t="s">
+      <c r="D17" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="32"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="35"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="32"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="29"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="35"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="35"/>
     </row>
     <row r="21" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
@@ -8235,13 +8262,13 @@
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
-      <c r="D29" s="43" t="s">
+      <c r="D29" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="45"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="44"/>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
@@ -8271,13 +8298,13 @@
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="49" t="s">
+      <c r="D32" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="51"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="48"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
@@ -8295,25 +8322,25 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="52" t="s">
+      <c r="D34" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="54"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="51"/>
     </row>
     <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="55" t="s">
+      <c r="D35" s="52" t="s">
         <v>199</v>
       </c>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="57"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="54"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
@@ -8337,13 +8364,13 @@
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="36" t="s">
+      <c r="D37" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="38"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="41"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
@@ -8403,13 +8430,13 @@
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="36" t="s">
+      <c r="D42" s="39" t="s">
         <v>372</v>
       </c>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="38"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="41"/>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
@@ -8427,25 +8454,25 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="36" t="s">
+      <c r="D44" s="39" t="s">
         <v>374</v>
       </c>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="38"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="41"/>
     </row>
     <row r="45" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
-      <c r="D45" s="36" t="s">
+      <c r="D45" s="39" t="s">
         <v>375</v>
       </c>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="38"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="41"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -8469,25 +8496,25 @@
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="36" t="s">
+      <c r="D47" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="38"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="41"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
-      <c r="D48" s="36" t="s">
+      <c r="D48" s="39" t="s">
         <v>157</v>
       </c>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="38"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="41"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
@@ -8499,61 +8526,61 @@
       <c r="C49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D49" s="46" t="s">
+      <c r="D49" s="55" t="s">
         <v>377</v>
       </c>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="48"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="57"/>
     </row>
     <row r="50" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="36" t="s">
+      <c r="D50" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="38"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="41"/>
     </row>
     <row r="51" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="36" t="s">
+      <c r="D51" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="37"/>
-      <c r="H51" s="38"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="41"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="36" t="s">
+      <c r="D52" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="37"/>
-      <c r="H52" s="38"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="41"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="36" t="s">
+      <c r="D53" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
-      <c r="G53" s="37"/>
-      <c r="H53" s="38"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="41"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
@@ -8569,6 +8596,39 @@
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
     <mergeCell ref="D27:H27"/>
     <mergeCell ref="D26:H26"/>
     <mergeCell ref="D8:H8"/>
@@ -8585,39 +8645,6 @@
     <mergeCell ref="D14:H14"/>
     <mergeCell ref="D22:H22"/>
     <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="D49:H49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8660,13 +8687,13 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -8696,37 +8723,37 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="33" t="s">
         <v>202</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="33" t="s">
         <v>203</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="35"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -8762,49 +8789,49 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="33" t="s">
         <v>244</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="33" t="s">
         <v>245</v>
       </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
     </row>
     <row r="14" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
@@ -8918,13 +8945,13 @@
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="43" t="s">
+      <c r="D22" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="45"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="44"/>
     </row>
     <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
@@ -9204,24 +9231,15 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
     <mergeCell ref="D34:H34"/>
     <mergeCell ref="D21:H21"/>
     <mergeCell ref="D22:H22"/>
@@ -9236,15 +9254,24 @@
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D27:H27"/>
     <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9285,13 +9312,13 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="39" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -9321,37 +9348,37 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="35"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="42"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -9387,61 +9414,61 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="35"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="33" t="s">
         <v>247</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="29"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
     </row>
     <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="29"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="35"/>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
@@ -9489,61 +9516,61 @@
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="35"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="32"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="35"/>
     </row>
     <row r="21" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="35"/>
     </row>
     <row r="22" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="29"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="35"/>
     </row>
     <row r="23" spans="1:8" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
@@ -9591,49 +9618,49 @@
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="32"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="29"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="33" t="s">
+      <c r="D27" s="30" t="s">
         <v>255</v>
       </c>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="35"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="32"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="29"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="35"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
-      <c r="D29" s="27" t="s">
+      <c r="D29" s="33" t="s">
         <v>257</v>
       </c>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="35"/>
     </row>
     <row r="30" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
@@ -9759,25 +9786,25 @@
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="36" t="s">
+      <c r="D39" s="39" t="s">
         <v>160</v>
       </c>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="38"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="41"/>
     </row>
     <row r="40" spans="1:8" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="36" t="s">
+      <c r="D40" s="39" t="s">
         <v>161</v>
       </c>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="38"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="41"/>
     </row>
     <row r="41" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
@@ -9949,41 +9976,6 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D46:H46"/>
     <mergeCell ref="D53:H53"/>
     <mergeCell ref="D14:H14"/>
     <mergeCell ref="D22:H22"/>
@@ -10000,6 +9992,41 @@
     <mergeCell ref="D24:H24"/>
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10063,13 +10090,13 @@
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="42"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -10243,25 +10270,25 @@
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="35"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="32"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="12"/>
@@ -10329,13 +10356,13 @@
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="43" t="s">
+      <c r="D24" s="42" t="s">
         <v>275</v>
       </c>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="44"/>
-      <c r="H24" s="45"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="44"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
@@ -10735,12 +10762,40 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
@@ -10753,40 +10808,12 @@
     <mergeCell ref="D16:H16"/>
     <mergeCell ref="D17:H17"/>
     <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Plantilla-modelo.xlsx
+++ b/Plantilla-modelo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollo-software\reporte-obras-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8C850D-6579-4502-9A74-026C682C149A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599AEAED-BD85-406F-BA53-4258366C8D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="947" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="947" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ANTEQUERA" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="393">
   <si>
     <t>REVISADO</t>
   </si>
@@ -278,18 +278,6 @@
     <t>4 - PRODUCTOS QUÍMICOS - NEUTRALIZADOR</t>
   </si>
   <si>
-    <t>1.4 Comprobación sinfín compactador:                           A  /                   Hz</t>
-  </si>
-  <si>
-    <t>1.5 Comprobación rototamiz:                                             A  /                   Hz</t>
-  </si>
-  <si>
-    <t>3.4 Caudal e intensidad Bomba 1                    A  /              Hz</t>
-  </si>
-  <si>
-    <t>3.5 Caudal e intensidad Bomba 2                A  /               Hz</t>
-  </si>
-  <si>
     <t>5.1 Comprobación de que las bombas dosifiquen producto. 
 ANOTAR CAUDALES E INTENSIDAD:
 Bomba dosificadora ácido:                 A  /                 Hz               %
@@ -343,18 +331,6 @@
     <t>3- SISTEMA DE BOMBEO (ARQUETA)</t>
   </si>
   <si>
-    <t>_________A</t>
-  </si>
-  <si>
-    <t>________m³/h</t>
-  </si>
-  <si>
-    <t>________A</t>
-  </si>
-  <si>
-    <t>_______m³/h</t>
-  </si>
-  <si>
     <t>3.6 Vaciar arqueta y obserbar el estado de mangueras, acoples, solidos en el fondo… (FOTOS)</t>
   </si>
   <si>
@@ -386,14 +362,6 @@
   </si>
   <si>
     <t>4. PRODUCTOS QUÍMICOS - NEUTRALIZADOR  DEPURADORA CAJAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1 Comprobación de que las bombas dosifiquen producto. 
-ANOTAR CAUDALES E INTENSIDAD:
-Bomba dosificadora ácido:                               A                   %
-Bomba dosificadora sosa:                                A                   %
-Bomba trasvase ácido:                                       A                  % 
-Bomba trasvase sosa:                                        A                  % </t>
   </si>
   <si>
     <t>4.2 Revisión de sensores  de niveles y recargar producto (FOTOS antes y después).</t>
@@ -539,12 +507,6 @@
   </si>
   <si>
     <t>14.3 Comprobar correcto funcionamiento bomba: sentido de giro y presión</t>
-  </si>
-  <si>
-    <t>14.4 Caudal e intensidad Bomba 1               A  /                 Hz</t>
-  </si>
-  <si>
-    <t>14.5 Caudal e intensidad Bomba 2               A   /                Hz</t>
   </si>
   <si>
     <r>
@@ -610,12 +572,6 @@
     <t>2 - SISTEMA DE BOMBEO (ARQUETA BOMBEO A)</t>
   </si>
   <si>
-    <t>6.3 Comprobar bomba 1 homogenizador a agua a tratar:                  A                       Hz</t>
-  </si>
-  <si>
-    <t>6.4 Comprobar bomba 2 homogenizador a agua a tratar:                  A                       Hz</t>
-  </si>
-  <si>
     <t>6.5 Vaciar neutralizador completamente y obserbar el estado de mangueras, acoples, solidos en el fondo… (FOTOS)</t>
   </si>
   <si>
@@ -705,158 +661,16 @@
 Bomba trasvase sosa:                  0,72 A   100%</t>
   </si>
   <si>
-    <t>1.4 Comprobación sinfín compactador:                        2,12   A  /         40       Hz</t>
-  </si>
-  <si>
-    <t>1.5 Comprobación rototamiz:                                     2,78       A  /          41,70      Hz</t>
-  </si>
-  <si>
     <t>2 - SISTEMA DE BOMBEO (ARQUETA GENERAL)</t>
   </si>
   <si>
-    <t>3.4 Caudal e intensidad Bomba 1               8         A     50       Hz</t>
-  </si>
-  <si>
-    <t>3.5 Caudal e intensidad Bomba 2               7,40     A  /       50        Hz</t>
-  </si>
-  <si>
-    <t>1.4 Comprobación sinfín compactador:                        1,04 A  /  51 Hz</t>
-  </si>
-  <si>
-    <t>1.5 Comprobación rototamiz                                          1,02 A  /  42,56 Hz</t>
-  </si>
-  <si>
-    <t>2.4 Caudal e intensidad Bomba 1                    9,25 A  /  50 Hz</t>
-  </si>
-  <si>
-    <t>2.5 Caudal e intensidad Bomba 2                    9,24 A  /  50  Hz</t>
-  </si>
-  <si>
-    <t>3.3 Comprobación soplante neutralizador:         2,25 A  y  0,3 Bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1 Comprobación de que las bombas dosifiquen producto. 
-ANATAR CAUDALES E INTENSIDAD:
-Bomba dosificadora ácido:                      0,69 A  y  25 %
-Bomba dosificadora sosa:                       0,69 A  y  25 %
-</t>
-  </si>
-  <si>
-    <t>1.4 Comprobación sinfín compactador:                    1,36  A  /        35   Hz</t>
-  </si>
-  <si>
-    <t>1.5 Comprobación rototamiz:                                     1,70   A  /      25     Hz</t>
-  </si>
-  <si>
-    <t>3.4 Caudal e intensidad Bomba 1            7,6   A  /    50    Hz</t>
-  </si>
-  <si>
-    <t>3.5 Caudal e intensidad Bomba 2            7,6    A  /        50  Hz</t>
-  </si>
-  <si>
     <t>2 - SISTEMA DE BOMBEO (ARQUETA LITRIS)</t>
   </si>
   <si>
-    <t>3.4 Caudal e intensidad Bomba 1            7,9  A  /    50    Hz</t>
-  </si>
-  <si>
-    <t>3.5 Caudal e intensidad Bomba 2            8,1    A  /        50  Hz</t>
-  </si>
-  <si>
-    <t>4.3 Comprobación soplante homogenizador:                  2,5   A  /          Bar / Nivel   23     %</t>
-  </si>
-  <si>
-    <t>4.4 Comprobación soplante neutralizador:                2,46   A  /         Bar / Nivel     18   %</t>
-  </si>
-  <si>
-    <t>5.4 Bomba dosificadora acido     0,85 A  50%</t>
-  </si>
-  <si>
     <t>5.5 Bomba dosificadora sosa       0,65A   50%</t>
   </si>
   <si>
-    <t>5.6 bomba trasvase acido        0,80A     100%</t>
-  </si>
-  <si>
-    <t>5.7  Bomba trasvase sosa        0,85A     100%</t>
-  </si>
-  <si>
     <t>6.4 Vaciar neutralizador completamente y obserbar el estado de mangueras, acoples, solidos en el fondo… (FOTOS)</t>
-  </si>
-  <si>
-    <t>6.2 Comprobación consumo bomba trasvase                 3,8 A  /     50   Hz</t>
-  </si>
-  <si>
-    <t>1.4 Comprobación sinfín compactador:                          2,2 A / 50 Hz</t>
-  </si>
-  <si>
-    <t>1.5 Comprobación rototamiz:                                          3,20 A / 35 Hz</t>
-  </si>
-  <si>
-    <t>1.4 Comprobación sinfín compactador:                        2,07 A   /   40 Hz</t>
-  </si>
-  <si>
-    <t>1.5 Comprobación rototamiz:                                         2,34 A   /  40 Hz</t>
-  </si>
-  <si>
-    <t>1.4 Comprobación sinfín compactador:                            1,45  A  /             50    Hz</t>
-  </si>
-  <si>
-    <t>1.5 Comprobación rototamiz:                                             1,99    A  /           50     Hz</t>
-  </si>
-  <si>
-    <t>2.4 Caudal e intensidad Bomba 1                         7,5     A  /       50    Hz</t>
-  </si>
-  <si>
-    <t>2.5 Caudal e intensidad Bomba 2                            7  A  /      50      Hz</t>
-  </si>
-  <si>
-    <t>3.3 Comprobación soplante homogenizador:             6    A  y   50HZ    10,7%</t>
-  </si>
-  <si>
-    <t>3.4 Comprobación soplante neutralizador:                 6,30   A  y    50HZ    31%</t>
-  </si>
-  <si>
-    <t>5.2 BOMBA TRASVASE           3,93 A    /    50HZ</t>
-  </si>
-  <si>
-    <t>6,2  Bomba recirculación       3,89  A      / 50  HZ</t>
-  </si>
-  <si>
-    <t>8.4 Comprobación rototamiz:                                      2,19    A  /      50  Hz</t>
-  </si>
-  <si>
-    <t>10.4 Aguitador reactor            1,65A     25hz</t>
-  </si>
-  <si>
-    <t>1.4 Comprobación sinfín compactador:                          2,10 A  /  35 Hz</t>
-  </si>
-  <si>
-    <t>1.5 Comprobación rototamiz:                                            2,30 A  /   35 Hz</t>
-  </si>
-  <si>
-    <t>6.2 Comprobación consumo bomba recirculación:           2,1 A  / 50 Hz</t>
-  </si>
-  <si>
-    <t>1.4 Comprobación sinfín compactador:                1,58 A  /  50 Hz</t>
-  </si>
-  <si>
-    <t>1.5 Comprobación rototamiz:                                 1,20 A  / 50  Hz</t>
-  </si>
-  <si>
-    <t>Bomba dosificadora acido      0,79 /   50 %</t>
-  </si>
-  <si>
-    <t>Bomba dosificadora sosa        0,79 /  50 %</t>
-  </si>
-  <si>
-    <t>Bomba trasvase acido                0,79  /  100 %</t>
-  </si>
-  <si>
-    <t>Bomba trasvase sosa                 0,79  /   100%</t>
-  </si>
-  <si>
-    <t>6.2 Comprobación consumo bomba recirculación:        2,2 A  / 50  Hz</t>
   </si>
   <si>
     <t>2.4 Caudal e intensidad Bomba 1</t>
@@ -917,14 +731,6 @@
     <t>5.2 comprobar consumo BOMBA TRASVASE:     3,30 A /   50 Hz</t>
   </si>
   <si>
-    <t>4.1 Comprobación de que las bombas dosifiquen producto. 
-ANATAR CAUDALES E INTENSIDAD:
-Bomba dosificadora ácido:                      0,72 A  y  50 %
-Bomba dosificadora sosa:                      0,72 A  y  50 %
-Bomba trasvase ácido:                          0,70 A  y  100 %
-Bomba trasvase sosa:                          0,80 A  y  100 %</t>
-  </si>
-  <si>
     <t>4.2 Revisión de  sensores  de niveles y recargar producto (FOTOS antes y después)</t>
   </si>
   <si>
@@ -934,27 +740,9 @@
     <t>3.2 Limpiar filtro aire soplante</t>
   </si>
   <si>
-    <t>3.3 Comprobación soplante homogenizador:                 2,15 A  y  20%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4 Comprobación soplante neutralizador:                     2,15 A  y  15% </t>
-  </si>
-  <si>
-    <t>2.4 Caudal e intensidad Bomba 1   8,2 A  / 50 Hz</t>
-  </si>
-  <si>
-    <t>2.5 Caudal e intensidad Bomba 2   8,2 A  / 50 Hz</t>
-  </si>
-  <si>
     <t>2.6 Vaciar arqueta  al máximo y obserbar el estado de mangueras, acoples, solidos en el fondo… (FOTOS)</t>
   </si>
   <si>
-    <t>2.4 Caudal e intensidad Bomba 1                    A  /              Hz</t>
-  </si>
-  <si>
-    <t>2.5 Caudal e intensidad Bomba 2                A  /               Hz</t>
-  </si>
-  <si>
     <t>2.6 Comprobar sentido de giro y estado de las aspas del agitador submarino.</t>
   </si>
   <si>
@@ -976,12 +764,6 @@
     <t>4.3 Comprobar correcto funcionamiento bomba: sentido de giro y presión</t>
   </si>
   <si>
-    <t>4.4 Caudal e intensidad Bomba 1                    A  /              Hz</t>
-  </si>
-  <si>
-    <t>4.5 Caudal e intensidad Bomba 2                A  /               Hz</t>
-  </si>
-  <si>
     <t>4.6 Vaciar arqueta  al máximo y obserbar el estado de mangueras, acoples, solidos en el fondo… (FOTOS)</t>
   </si>
   <si>
@@ -992,9 +774,6 @@
   </si>
   <si>
     <t>5.2 Limpiar filtro aire soplante</t>
-  </si>
-  <si>
-    <t>5.3 Comprobación soplante homogenizador:                        A  /          Bar / Nivel        %</t>
   </si>
   <si>
     <t>5.5 Comprobar estado de las mangueras de aire.</t>
@@ -1126,54 +905,15 @@
     <t>1.3 Comprobar correcto funcionamiento bomba: sentido de giro y presión</t>
   </si>
   <si>
-    <t>1.4 Caudal e intensidad Bomba 1                    A  /              Hz</t>
-  </si>
-  <si>
-    <t>1.5 Caudal e intensidad Bomba 2                A  /               Hz</t>
-  </si>
-  <si>
-    <t>4.3 Bomba dosificadora acido          0,81 A   /     50 %</t>
-  </si>
-  <si>
-    <t>4.4 Bomba dosificadora sosa          0,82 A    /     50 %</t>
-  </si>
-  <si>
-    <t>4.5 Bomba trasvase acido         0,82 A     /     100%</t>
-  </si>
-  <si>
-    <t>4.6 bomba trasvase sosa       0,85 A      /     100%</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.7 Revisar que el nivel coincide con el representado en la pantalla HMI. </t>
   </si>
   <si>
-    <t>2.4 Caudal e intensidad Bomba 1              6,9 A   /   49,84 Hz</t>
-  </si>
-  <si>
-    <t>2.5 Caudal e intensidad Bomba 2              6,9 A   /   49,25 Hz</t>
-  </si>
-  <si>
     <t>2.6 Vaciar arqueta  al máximo y obserbar el estado de mangueras, acoples, solidos en el fondo…</t>
   </si>
   <si>
-    <t>3.3 Comprobación soplante neutralizador 1:             2 A    /  50HZ</t>
-  </si>
-  <si>
-    <t>3.4 Comprobación soplante neutralizador 2:               7,1 A    / 68,2%   /  40 Hz</t>
-  </si>
-  <si>
-    <t>4.1 Comprobación de que las bombas dosifiquen producto. 
-ANATAR CAUDALES E INTENSIDAD:         
-Bomba  dosificadora ácido neutralizador:             0,78 A   /   ____ Hz/ 50 %
-Bomba dosificadora sosa neutralizador :              0,79 A   /    ____ Hz / 50%</t>
-  </si>
-  <si>
     <t>5.3 Vaciar neutralizador 1 completamente y obserbar el estado de mangueras, acoples, solidos en el fondo… (FOTOS)</t>
   </si>
   <si>
-    <t>6.2 Comprobación consumo bomba recirculación:            3,70 A  50 Hz</t>
-  </si>
-  <si>
     <t>3 - SISTEMA DE BOMBEO (ARQUETA PALETS)</t>
   </si>
   <si>
@@ -1207,32 +947,15 @@
     <t>4 - SISTEMA DE BOMBEO (ARQUETA PALETS)</t>
   </si>
   <si>
-    <t>4.4 Caudal e intensidad Bomba 1                 7,4       A      50      Hz</t>
-  </si>
-  <si>
     <t>5 - SOPLANTES - HOMOGENEIZADOR Y NEUTRALIZADOR</t>
   </si>
   <si>
     <t>5.1 Comprobar que los difusores reparte el aire por igual y que no esten rotos</t>
   </si>
   <si>
-    <t>5.3 Comprobación soplante homogenizador:  6,22  A    40,21HZ    23,3%</t>
-  </si>
-  <si>
-    <t>5.4 Comprobación soplante neutralizador:     6,30 A     40,34HZ     26,9%</t>
-  </si>
-  <si>
     <t>6 - PRODUCTOS QUÍMICOS</t>
   </si>
   <si>
-    <t>6.1 Comprobación de que las bombas dosifiquen producto. 
-ANATAR CAUDALES E INTENSIDAD:
-Bomba dosificadora ácido:          0,71 A   50%
-Bomba dosificadora sosa:           0,71 A    50%
-Bomba trasvase ácido:                 0,72 A   100%
-Bomba trasvase sosa:                  0,75 A   100%</t>
-  </si>
-  <si>
     <t>6.2 Revisión de  sensores  de niveles y recargar producto.</t>
   </si>
   <si>
@@ -1245,28 +968,16 @@
     <t>7.3 Vaciar neutralizador completamente y obserbar el estado de mangueras, acoples, solidos en el fondo… (FOTOS)</t>
   </si>
   <si>
-    <t>7.4 Intensidad bomba trasvase    3,76A    50HZ</t>
-  </si>
-  <si>
     <t>8 - NEUTRALIZADOR</t>
   </si>
   <si>
     <t>8.1Revisar que el nivel coincide con el representado en la pantalla HMI.</t>
   </si>
   <si>
-    <t>8.2 Comprobación consumo bomba recirculación:                 3,40A  /     50Hz</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.3 Comprobar que el equipo funciona sin anomalías. </t>
   </si>
   <si>
-    <t>8.4 Vaciar neutralizador 2 completamente y obserbar el estado de mangueras, acoples, solidos en el fondo… (FOTOS)</t>
-  </si>
-  <si>
     <t>9 - CONTROLADOR PH - NEUTRALIZADOR</t>
-  </si>
-  <si>
-    <t>9.1 Limpiar sondas (foto)</t>
   </si>
   <si>
     <t>9.2 Calibar sondas.</t>
@@ -1316,38 +1027,6 @@
   </si>
   <si>
     <t>7.5 Verificar seguridades (FOTOS del cuadro antes y después)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3 Comprobación soplante homogenizador:       2,10 A  /   20% </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4 Comprobación soplante neutralizador:               2,05 A  /   15% </t>
-  </si>
-  <si>
-    <t>4.1 Comprobación de que las bombas dosifiquen producto. 
-ANOTAR CAUDALES E INTENSIDAD:
-Bomba dosificadora ácido:          0,78 A  / 50 %
-Bomba dosificadora sosa:           0,71 A  / 50 %
-Bomba trasvase ácido:                 0,67 A  / 100 %
-Bomba trasvase sosa:                  0,66 A  / 100 %</t>
-  </si>
-  <si>
-    <t>2.4 Caudal e intensidad Bomba 1             5,50 A  / 48,9 Hz</t>
-  </si>
-  <si>
-    <t>2.5 Caudal e intensidad Bomba 2            5,6  A  /  50 Hz</t>
-  </si>
-  <si>
-    <t>2.4 Caudal e intensidad Bomba 1              7,6 A  /  49,88 Hz</t>
-  </si>
-  <si>
-    <t>2.5 Caudal e intensidad Bomba 2              7,9  A  /  49,6 Hz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3 Comprobación soplante homogenizador:  5,02 A /  25 Hz / </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4 Comprobación soplante neutralizador:   4,6 A / 25 Hz / </t>
   </si>
   <si>
     <t xml:space="preserve">4.1 Comprobación de que las bombas dosifiquen producto. 
@@ -1364,9 +1043,6 @@
     <t>7.1Revisar que el nivel coincide con el representado en la pantalla HMI.</t>
   </si>
   <si>
-    <t>7.2 Comprobación consumo bomba recirculación:              4,15   A  /      50    Hz</t>
-  </si>
-  <si>
     <t xml:space="preserve">7.3 Comprobar que el equipo funciona sin anomalías. </t>
   </si>
   <si>
@@ -1379,15 +1055,6 @@
     <t>9 - CUADRO ELÉCTRICO</t>
   </si>
   <si>
-    <t>6.2 comprobar consumo BOMBA RECIRUCLACION:   3,20 A /  50  Hz</t>
-  </si>
-  <si>
-    <t>2.4 Caudal e intensidad Bomba 1               6,95         A      50      Hz</t>
-  </si>
-  <si>
-    <t>2.5 Caudal e intensidad Bomba 2               6,75     A  /      50         Hz</t>
-  </si>
-  <si>
     <t>1.6 Vaciar arqueta  al máximo y obserbar el estado de mangueras, acoples, solidos en el fondo… (FOTOS)</t>
   </si>
   <si>
@@ -1398,12 +1065,6 @@
   </si>
   <si>
     <t xml:space="preserve">4 - CUADRO ELÉCTRICO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1 Comprobar bomba grupo presión 1:             A                   Hz </t>
-  </si>
-  <si>
-    <t>2.2  Comprobar bomba grupo presión 2:             A                   Hz</t>
   </si>
   <si>
     <t xml:space="preserve">4.1 Eliminar y consignar las fuentes de energía al cuadro para realizar su 
@@ -1422,16 +1083,367 @@
     <t>4.5 Verificar seguridades (FOTOS del cuadro antes y después).</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1 Comprobar bomba grupo presión 1:             A                   Hz </t>
-  </si>
-  <si>
-    <t>3.2  Comprobar bomba grupo presión 2:             A                   Hz</t>
-  </si>
-  <si>
     <t>4.1 Esta tarea es una prueba para ver si funciona el script</t>
   </si>
   <si>
     <t>1.7 Esta tarea es una prueba para ver si funciona el script</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4 Comprobación sinfín compactador:                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 Comprobación rototamiz:                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4 Caudal e intensidad Bomba 1             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 Caudal e intensidad Bomba 2            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3 Comprobación soplante homogenizador:      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4 Comprobación soplante neutralizador:               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2 Comprobación consumo bomba recirculación:           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1 Comprobación de que las bombas dosifiquen producto. 
+ANOTAR CAUDALES E INTENSIDAD:
+Bomba dosificadora ácido:          
+Bomba dosificadora sosa:           
+Bomba trasvase ácido:                
+Bomba trasvase sosa:                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4 Comprobación sinfín compactador:                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 Comprobación rototamiz:                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4 Caudal e intensidad Bomba 1               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 Caudal e intensidad Bomba 2               </t>
+  </si>
+  <si>
+    <t>2.6 Vaciar arqueta  al máximo y observar el estado de mangueras, acoples, solidos en el fondo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4 Caudal e intensidad Bomba 1              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5 Caudal e intensidad Bomba 2               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4 Caudal e intensidad Bomba 1                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3 Comprobación soplante homogenizador:  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4 Comprobación soplante neutralizador:     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1 Comprobación de que las bombas dosifiquen producto. 
+ANATAR CAUDALES E INTENSIDAD:
+Bomba dosificadora ácido:          
+Bomba dosificadora sosa:           
+Bomba trasvase ácido:                
+Bomba trasvase sosa:                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4 Intensidad bomba trasvase    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2 Comprobación consumo bomba recirculación:         </t>
+  </si>
+  <si>
+    <t>8.4 Vaciar neutralizador 2 completamente y obserbar el estado de mangueras, acoples, solidos en el fondo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1 Limpiar sondas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4 Comprobación sinfín compactador:                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 Comprobación rototamiz                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4 Caudal e intensidad Bomba 1                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 Caudal e intensidad Bomba 2                    </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2.6 </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Vaciar arqueta  al máximo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> y obserbar el estado de mangueras, acoples, solidos en el fondo</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3 Comprobación soplante neutralizador:        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1 Comprobación de que las bombas dosifiquen producto. 
+ANATAR CAUDALES E INTENSIDAD:
+Bomba dosificadora ácido:                      
+Bomba dosificadora sosa:                       
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4 Comprobación sinfín compactador:                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 Comprobación rototamiz:                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4 Caudal e intensidad Bomba 1              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 Caudal e intensidad Bomba 2              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3 Comprobación soplante homogenizador:  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4 Comprobación soplante neutralizador:   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bomba dosificadora acido      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bomba dosificadora sosa        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bomba trasvase acido                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bomba trasvase sosa                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2 Comprobación consumo bomba recirculación:        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4 Comprobación sinfín compactador:                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 Comprobación rototamiz:                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4 Caudal e intensidad Bomba 1            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5 Caudal e intensidad Bomba 2            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3 Comprobación soplante homogenizador:                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4 Comprobación soplante neutralizador:               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4 Bomba dosificadora acido     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6 bomba trasvase acido  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7  Bomba trasvase sosa        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2 Comprobación consumo bomba recirculación:             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2 Comprobación consumo bomba trasvase               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4 Comprobación sinfín compactador:                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 Comprobación rototamiz:                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4 Caudal e intensidad Bomba 1  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 Caudal e intensidad Bomba 2  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3 Comprobación soplante homogenizador:              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4 Comprobación soplante neutralizador:            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1 Comprobación de que las bombas dosifiquen producto. 
+ANATAR CAUDALES E INTENSIDAD:
+Bomba dosificadora ácido:                     
+Bomba dosificadora sosa:                   
+Bomba trasvase ácido:                  
+Bomba trasvase sosa:                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2 comprobar consumo BOMBA RECIRUCLACION:   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4 Caudal e intensidad Bomba 1                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5 Caudal e intensidad Bomba 2         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4 Caudal e intensidad Bomba 1               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5 Caudal e intensidad Bomba 2           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3 Comprobación soplante homogenizador:              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3 Comprobar bomba 1 homogenizador a agua a tratar:            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4 Comprobar bomba 2 homogenizador a agua a tratar:               </t>
+  </si>
+  <si>
+    <t>J60:J61J60:K62J60:K63J60:L64J60:M64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4 Caudal e intensidad Bomba 1          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 Caudal e intensidad Bomba 2           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1 Comprobar bomba grupo presión 1:           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2  Comprobar bomba grupo presión 2:         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1 Comprobar bomba grupo presión 1:            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2  Comprobar bomba grupo presión 2:          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4 Comprobación sinfín compactador:                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 Comprobación rototamiz:                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4 Caudal e intensidad Bomba 1                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 Caudal e intensidad Bomba 2                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3 Comprobación soplante homogenizador:          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4 Comprobación soplante neutralizador:                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1 Comprobación de que las bombas dosifiquen producto. 
+ANOTAR CAUDALES E INTENSIDAD:
+Bomba dosificadora ácido:                              
+Bomba dosificadora sosa:                               
+Bomba trasvase ácido:                                     
+Bomba trasvase sosa:                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6 bomba trasvase sosa       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5 Bomba trasvase acido         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3 Bomba dosificadora acido          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4 Bomba dosificadora sosa          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2 BOMBA TRASVASE         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,2  Bomba recirculación      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4 Comprobación rototamiz:                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4 Aguitador reactor          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4 Caudal e intensidad Bomba 1         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5 Caudal e intensidad Bomba 2              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 Comprobación rototamiz:                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4 Caudal e intensidad Bomba 1        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 Caudal e intensidad Bomba 2        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3 Comprobación soplante neutralizador 1:          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4 Comprobación soplante neutralizador 2:             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1 Comprobación de que las bombas dosifiquen producto. 
+ANATAR CAUDALES E INTENSIDAD:         
+Bomba  dosificadora ácido neutralizador:             
+Bomba dosificadora sosa neutralizador :             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4 Caudal e intensidad Bomba 1                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 Caudal e intensidad Bomba 2            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1 Comprobar bomba grupo presión 1:          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2  Comprobar bomba grupo presión 2:          </t>
+  </si>
+  <si>
+    <t>4.5 Verificar seguridades (FOTOS del cuadro antes y después) prueba</t>
   </si>
 </sst>
 </file>
@@ -1636,6 +1648,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1644,6 +1665,24 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1663,38 +1702,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1722,15 +1743,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -2098,25 +2110,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -2146,13 +2158,13 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -2164,13 +2176,13 @@
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="26"/>
+      <c r="D6" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="29"/>
     </row>
     <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
@@ -2188,37 +2200,37 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="32"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="41"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="4" t="s">
-        <v>226</v>
+        <v>167</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="H10" s="8"/>
     </row>
@@ -2227,12 +2239,12 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="9" t="s">
-        <v>227</v>
+        <v>168</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -2241,7 +2253,7 @@
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="21" t="s">
-        <v>228</v>
+        <v>169</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
@@ -2258,13 +2270,13 @@
       <c r="C13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="26"/>
+      <c r="D13" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="29"/>
     </row>
     <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
@@ -2282,25 +2294,25 @@
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="38"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="32"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
@@ -2312,7 +2324,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="H17" s="8"/>
     </row>
@@ -2326,7 +2338,7 @@
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="H18" s="11"/>
     </row>
@@ -2335,7 +2347,7 @@
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="21" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="22"/>
@@ -2352,20 +2364,20 @@
       <c r="C20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="24" t="s">
-        <v>316</v>
-      </c>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="26"/>
+      <c r="D20" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="21" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
@@ -2389,7 +2401,7 @@
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="21" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="22"/>
@@ -2401,7 +2413,7 @@
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="21" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -2430,25 +2442,25 @@
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="26"/>
+      <c r="D26" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="29"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="44"/>
+      <c r="D27" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="32"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
@@ -2484,13 +2496,13 @@
       <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D30" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="26"/>
+      <c r="D30" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="29"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
@@ -2520,25 +2532,25 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="D33" s="36" t="s">
-        <v>169</v>
-      </c>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="38"/>
+      <c r="D33" s="43" t="s">
+        <v>156</v>
+      </c>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="45"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="14"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="39" t="s">
-        <v>323</v>
-      </c>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="41"/>
+      <c r="D34" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="26"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
@@ -2550,20 +2562,20 @@
       <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="26"/>
+      <c r="D35" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="29"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="21" t="s">
-        <v>319</v>
+        <v>238</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
@@ -2575,7 +2587,7 @@
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="21" t="s">
-        <v>320</v>
+        <v>239</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="22"/>
@@ -2587,7 +2599,7 @@
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="21" t="s">
-        <v>321</v>
+        <v>240</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="22"/>
@@ -2598,13 +2610,13 @@
       <c r="A39" s="13"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="39" t="s">
-        <v>322</v>
-      </c>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="41"/>
+      <c r="D39" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="26"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
@@ -2616,13 +2628,13 @@
       <c r="C40" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="24" t="s">
+      <c r="D40" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="26"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="29"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
@@ -2641,7 +2653,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="21" t="s">
-        <v>229</v>
+        <v>170</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
@@ -2658,32 +2670,32 @@
       <c r="C43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D43" s="24" t="s">
+      <c r="D43" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="26"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="29"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="27" t="s">
-        <v>230</v>
-      </c>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="29"/>
+      <c r="D44" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="38"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="21" t="s">
-        <v>232</v>
+        <v>173</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="22"/>
@@ -2695,7 +2707,7 @@
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="21" t="s">
-        <v>231</v>
+        <v>172</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
@@ -2707,7 +2719,7 @@
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="21" t="s">
-        <v>233</v>
+        <v>174</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="22"/>
@@ -2719,7 +2731,7 @@
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="21" t="s">
-        <v>234</v>
+        <v>175</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
@@ -2757,32 +2769,6 @@
     <row r="282" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D16:H16"/>
@@ -2799,6 +2785,32 @@
     <mergeCell ref="D26:H26"/>
     <mergeCell ref="D27:H27"/>
     <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D43:H43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2826,20 +2838,20 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="D1" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="21" t="s">
-        <v>297</v>
+        <v>228</v>
       </c>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
@@ -2850,32 +2862,32 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="29"/>
+      <c r="D3" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="38"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="32"/>
+      <c r="D4" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="33" t="s">
-        <v>300</v>
+        <v>359</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
@@ -2887,7 +2899,7 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="33" t="s">
-        <v>301</v>
+        <v>360</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -2899,7 +2911,7 @@
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="21" t="s">
-        <v>381</v>
+        <v>279</v>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
@@ -2916,20 +2928,20 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>382</v>
-      </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
+      <c r="D8" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="21" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
@@ -2941,7 +2953,7 @@
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="21" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
@@ -2958,20 +2970,20 @@
       <c r="C11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="24" t="s">
-        <v>383</v>
-      </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="26"/>
+      <c r="D11" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="21" t="s">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
@@ -2983,7 +2995,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="21" t="s">
-        <v>393</v>
+        <v>364</v>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
@@ -3000,20 +3012,20 @@
       <c r="C14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>384</v>
-      </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="26"/>
+      <c r="D14" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="29"/>
     </row>
     <row r="15" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="21" t="s">
-        <v>387</v>
+        <v>283</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
@@ -3025,7 +3037,7 @@
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="21" t="s">
-        <v>388</v>
+        <v>284</v>
       </c>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
@@ -3037,7 +3049,7 @@
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="21" t="s">
-        <v>389</v>
+        <v>285</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
@@ -3049,7 +3061,7 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="21" t="s">
-        <v>390</v>
+        <v>286</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -3061,7 +3073,7 @@
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="21" t="s">
-        <v>391</v>
+        <v>287</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="22"/>
@@ -3070,6 +3082,13 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="D8:H8"/>
@@ -3082,13 +3101,6 @@
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3119,25 +3131,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="D1" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -3155,49 +3167,49 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="38"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="45"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
+      <c r="D5" s="43" t="s">
+        <v>365</v>
+      </c>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="38"/>
+      <c r="D6" s="43" t="s">
+        <v>366</v>
+      </c>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="45"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -3209,13 +3221,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
+      <c r="D8" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -3233,32 +3245,32 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="29"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="38"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="33" t="s">
-        <v>208</v>
+        <v>367</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
@@ -3270,7 +3282,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="33" t="s">
-        <v>209</v>
+        <v>368</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
@@ -3299,13 +3311,13 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
+      <c r="D15" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
@@ -3336,7 +3348,7 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="21" t="s">
-        <v>210</v>
+        <v>369</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -3348,7 +3360,7 @@
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="21" t="s">
-        <v>211</v>
+        <v>370</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="22"/>
@@ -3360,7 +3372,7 @@
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="21" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
@@ -3377,97 +3389,97 @@
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="26"/>
+      <c r="D21" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="29"/>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="41"/>
+      <c r="D22" s="24" t="s">
+        <v>371</v>
+      </c>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="12"/>
-      <c r="D23" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="41"/>
+      <c r="D23" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="26"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="39" t="s">
-        <v>302</v>
-      </c>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="41"/>
+      <c r="D24" s="24" t="s">
+        <v>374</v>
+      </c>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="26"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="12"/>
-      <c r="D25" s="39" t="s">
-        <v>303</v>
-      </c>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="41"/>
+      <c r="D25" s="24" t="s">
+        <v>375</v>
+      </c>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="26"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="12"/>
-      <c r="D26" s="39" t="s">
-        <v>304</v>
-      </c>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="41"/>
+      <c r="D26" s="24" t="s">
+        <v>373</v>
+      </c>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="26"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="12"/>
-      <c r="D27" s="39" t="s">
-        <v>305</v>
-      </c>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="41"/>
+      <c r="D27" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="26"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="12"/>
-      <c r="D28" s="39" t="s">
-        <v>306</v>
-      </c>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="41"/>
+      <c r="D28" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="26"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -3479,20 +3491,20 @@
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="26"/>
+      <c r="D29" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="29"/>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="21" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -3503,20 +3515,20 @@
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="39" t="s">
-        <v>212</v>
-      </c>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="41"/>
+      <c r="D31" s="24" t="s">
+        <v>376</v>
+      </c>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="26"/>
     </row>
     <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="21" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -3528,7 +3540,7 @@
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="21" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E33" s="22"/>
       <c r="F33" s="22"/>
@@ -3545,13 +3557,13 @@
       <c r="C34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="26"/>
+      <c r="D34" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="29"/>
     </row>
     <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
@@ -3570,7 +3582,7 @@
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="21" t="s">
-        <v>213</v>
+        <v>377</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
@@ -3594,7 +3606,7 @@
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="21" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="22"/>
@@ -3611,20 +3623,20 @@
       <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D39" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="26"/>
+      <c r="D39" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="29"/>
     </row>
     <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="21" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
@@ -3653,20 +3665,20 @@
       <c r="C42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D42" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="26"/>
+      <c r="D42" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="29"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="58" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E43" s="58"/>
       <c r="F43" s="58"/>
@@ -3677,20 +3689,20 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="38"/>
+      <c r="D44" s="43" t="s">
+        <v>102</v>
+      </c>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="45"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="3" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -3701,25 +3713,25 @@
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="36" t="s">
-        <v>214</v>
-      </c>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="37"/>
-      <c r="H46" s="38"/>
+      <c r="D46" s="43" t="s">
+        <v>378</v>
+      </c>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="45"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="38"/>
+      <c r="D47" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="E47" s="44"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="45"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
@@ -3731,20 +3743,20 @@
       <c r="C48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D48" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="26"/>
+      <c r="D48" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="29"/>
     </row>
     <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="21" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="22"/>
@@ -3756,7 +3768,7 @@
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="21" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E50" s="22"/>
       <c r="F50" s="22"/>
@@ -3768,7 +3780,7 @@
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="21" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="22"/>
@@ -3785,20 +3797,20 @@
       <c r="C52" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D52" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="26"/>
+      <c r="D52" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="29"/>
     </row>
     <row r="53" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="21" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E53" s="22"/>
       <c r="F53" s="22"/>
@@ -3810,7 +3822,7 @@
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="21" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="22"/>
@@ -3822,7 +3834,7 @@
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="21" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="22"/>
@@ -3834,7 +3846,7 @@
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="21" t="s">
-        <v>215</v>
+        <v>379</v>
       </c>
       <c r="E56" s="22"/>
       <c r="F56" s="22"/>
@@ -3851,32 +3863,32 @@
       <c r="C57" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
-      <c r="H57" s="26"/>
+      <c r="D57" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="29"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="E58" s="43"/>
-      <c r="F58" s="43"/>
-      <c r="G58" s="43"/>
-      <c r="H58" s="44"/>
+      <c r="D58" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="32"/>
     </row>
     <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="21" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E59" s="22"/>
       <c r="F59" s="22"/>
@@ -3888,7 +3900,7 @@
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="21" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
@@ -3900,7 +3912,7 @@
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="21" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="E61" s="22"/>
       <c r="F61" s="22"/>
@@ -3917,20 +3929,20 @@
       <c r="C62" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D62" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
-      <c r="H62" s="26"/>
+      <c r="D62" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="E62" s="28"/>
+      <c r="F62" s="28"/>
+      <c r="G62" s="28"/>
+      <c r="H62" s="29"/>
     </row>
     <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="21" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E63" s="22"/>
       <c r="F63" s="22"/>
@@ -3942,7 +3954,7 @@
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="21" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E64" s="22"/>
       <c r="F64" s="22"/>
@@ -3954,7 +3966,7 @@
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="21" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E65" s="22"/>
       <c r="F65" s="22"/>
@@ -3966,7 +3978,7 @@
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="21" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E66" s="22"/>
       <c r="F66" s="22"/>
@@ -3978,7 +3990,7 @@
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="21" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E67" s="22"/>
       <c r="F67" s="22"/>
@@ -3990,7 +4002,7 @@
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="21" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E68" s="22"/>
       <c r="F68" s="22"/>
@@ -4002,7 +4014,7 @@
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="21" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E69" s="22"/>
       <c r="F69" s="22"/>
@@ -4014,7 +4026,7 @@
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="21" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="E70" s="22"/>
       <c r="F70" s="22"/>
@@ -4026,7 +4038,7 @@
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="21" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E71" s="22"/>
       <c r="F71" s="22"/>
@@ -4038,7 +4050,7 @@
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="21" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E72" s="22"/>
       <c r="F72" s="22"/>
@@ -4055,13 +4067,13 @@
       <c r="C73" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
-      <c r="H73" s="26"/>
+      <c r="D73" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="29"/>
     </row>
     <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="2"/>
@@ -4116,7 +4128,7 @@
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="21" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E78" s="22"/>
       <c r="F78" s="22"/>
@@ -4133,20 +4145,20 @@
       <c r="C79" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D79" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="E79" s="25"/>
-      <c r="F79" s="25"/>
-      <c r="G79" s="25"/>
-      <c r="H79" s="26"/>
+      <c r="D79" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="E79" s="28"/>
+      <c r="F79" s="28"/>
+      <c r="G79" s="28"/>
+      <c r="H79" s="29"/>
     </row>
     <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="21" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E80" s="22"/>
       <c r="F80" s="22"/>
@@ -4157,32 +4169,32 @@
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
-      <c r="D81" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="E81" s="28"/>
-      <c r="F81" s="28"/>
-      <c r="G81" s="28"/>
-      <c r="H81" s="29"/>
+      <c r="D81" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="E81" s="37"/>
+      <c r="F81" s="37"/>
+      <c r="G81" s="37"/>
+      <c r="H81" s="38"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
-      <c r="D82" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="E82" s="31"/>
-      <c r="F82" s="31"/>
-      <c r="G82" s="31"/>
-      <c r="H82" s="32"/>
+      <c r="D82" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="E82" s="40"/>
+      <c r="F82" s="40"/>
+      <c r="G82" s="40"/>
+      <c r="H82" s="41"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="33" t="s">
-        <v>144</v>
+        <v>380</v>
       </c>
       <c r="E83" s="34"/>
       <c r="F83" s="34"/>
@@ -4194,7 +4206,7 @@
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="33" t="s">
-        <v>145</v>
+        <v>381</v>
       </c>
       <c r="E84" s="34"/>
       <c r="F84" s="34"/>
@@ -4205,13 +4217,13 @@
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
-      <c r="D85" s="27" t="s">
-        <v>146</v>
-      </c>
-      <c r="E85" s="28"/>
-      <c r="F85" s="28"/>
-      <c r="G85" s="28"/>
-      <c r="H85" s="29"/>
+      <c r="D85" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="E85" s="37"/>
+      <c r="F85" s="37"/>
+      <c r="G85" s="37"/>
+      <c r="H85" s="38"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
@@ -4223,20 +4235,20 @@
       <c r="C86" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D86" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="E86" s="25"/>
-      <c r="F86" s="25"/>
-      <c r="G86" s="25"/>
-      <c r="H86" s="26"/>
+      <c r="D86" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="E86" s="28"/>
+      <c r="F86" s="28"/>
+      <c r="G86" s="28"/>
+      <c r="H86" s="29"/>
     </row>
     <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="21" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E87" s="22"/>
       <c r="F87" s="22"/>
@@ -4248,7 +4260,7 @@
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="21" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E88" s="22"/>
       <c r="F88" s="22"/>
@@ -4260,7 +4272,7 @@
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="21" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E89" s="22"/>
       <c r="F89" s="22"/>
@@ -4272,7 +4284,7 @@
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="21" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E90" s="22"/>
       <c r="F90" s="22"/>
@@ -4284,7 +4296,7 @@
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="21" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E91" s="22"/>
       <c r="F91" s="22"/>
@@ -4293,6 +4305,79 @@
     </row>
   </sheetData>
   <mergeCells count="89">
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D73:H73"/>
+    <mergeCell ref="D62:H62"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D56:H56"/>
+    <mergeCell ref="D57:H57"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="D61:H61"/>
+    <mergeCell ref="D90:H90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="D86:H86"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="D76:H76"/>
+    <mergeCell ref="D77:H77"/>
+    <mergeCell ref="D78:H78"/>
+    <mergeCell ref="D79:H79"/>
+    <mergeCell ref="D80:H80"/>
+    <mergeCell ref="D81:H81"/>
+    <mergeCell ref="D82:H82"/>
+    <mergeCell ref="D83:H83"/>
+    <mergeCell ref="D84:H84"/>
+    <mergeCell ref="D85:H85"/>
     <mergeCell ref="D31:H31"/>
     <mergeCell ref="D36:H36"/>
     <mergeCell ref="D87:H87"/>
@@ -4309,79 +4394,6 @@
     <mergeCell ref="D70:H70"/>
     <mergeCell ref="D71:H71"/>
     <mergeCell ref="D72:H72"/>
-    <mergeCell ref="D90:H90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="D86:H86"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="D76:H76"/>
-    <mergeCell ref="D77:H77"/>
-    <mergeCell ref="D78:H78"/>
-    <mergeCell ref="D79:H79"/>
-    <mergeCell ref="D80:H80"/>
-    <mergeCell ref="D81:H81"/>
-    <mergeCell ref="D82:H82"/>
-    <mergeCell ref="D83:H83"/>
-    <mergeCell ref="D84:H84"/>
-    <mergeCell ref="D85:H85"/>
-    <mergeCell ref="D73:H73"/>
-    <mergeCell ref="D62:H62"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D56:H56"/>
-    <mergeCell ref="D57:H57"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="D61:H61"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4411,25 +4423,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -4460,7 +4472,7 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="33" t="s">
-        <v>204</v>
+        <v>331</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
@@ -4472,7 +4484,7 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="33" t="s">
-        <v>205</v>
+        <v>382</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -4483,13 +4495,13 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -4501,13 +4513,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -4525,32 +4537,32 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="29"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="38"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="33" t="s">
-        <v>307</v>
+        <v>383</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
@@ -4562,7 +4574,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="33" t="s">
-        <v>308</v>
+        <v>384</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
@@ -4574,7 +4586,7 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="21" t="s">
-        <v>309</v>
+        <v>232</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
@@ -4591,20 +4603,20 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
+      <c r="D15" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="21" t="s">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
@@ -4616,7 +4628,7 @@
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="21" t="s">
-        <v>241</v>
+        <v>181</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
@@ -4628,7 +4640,7 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="21" t="s">
-        <v>310</v>
+        <v>385</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -4640,7 +4652,7 @@
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="21" t="s">
-        <v>311</v>
+        <v>386</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="22"/>
@@ -4652,7 +4664,7 @@
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="21" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
@@ -4669,32 +4681,32 @@
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="26"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="29"/>
     </row>
     <row r="22" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="44"/>
+      <c r="D22" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="21" t="s">
-        <v>239</v>
+        <v>179</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="22"/>
@@ -4706,7 +4718,7 @@
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="21" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -4723,20 +4735,20 @@
       <c r="C25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="26"/>
+      <c r="D25" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="29"/>
     </row>
     <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="21" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
@@ -4748,7 +4760,7 @@
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="21" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
@@ -4760,7 +4772,7 @@
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="21" t="s">
-        <v>313</v>
+        <v>233</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -4777,13 +4789,13 @@
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="26"/>
+      <c r="D29" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="29"/>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
@@ -4802,7 +4814,7 @@
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="21" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="22"/>
@@ -4843,13 +4855,13 @@
       <c r="C34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="26"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="29"/>
     </row>
     <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
@@ -4885,20 +4897,20 @@
       <c r="C37" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="24" t="s">
+      <c r="D37" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="26"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="29"/>
     </row>
     <row r="38" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="21" t="s">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="22"/>
@@ -4910,7 +4922,7 @@
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="21" t="s">
-        <v>232</v>
+        <v>173</v>
       </c>
       <c r="E39" s="22"/>
       <c r="F39" s="22"/>
@@ -4922,7 +4934,7 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="21" t="s">
-        <v>271</v>
+        <v>202</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
@@ -4934,7 +4946,7 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="21" t="s">
-        <v>272</v>
+        <v>203</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
@@ -4946,7 +4958,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="21" t="s">
-        <v>273</v>
+        <v>204</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
@@ -4955,16 +4967,24 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="D21:H21"/>
     <mergeCell ref="D22:H22"/>
@@ -4977,24 +4997,16 @@
     <mergeCell ref="D29:H29"/>
     <mergeCell ref="D30:H30"/>
     <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5002,7 +5014,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B6D5BD9-6748-4A03-A6F1-166697746BD8}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -5015,20 +5027,20 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="D1" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="21" t="s">
-        <v>297</v>
+        <v>228</v>
       </c>
       <c r="E2" s="22"/>
       <c r="F2" s="22"/>
@@ -5039,32 +5051,32 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="29"/>
+      <c r="D3" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="38"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="32"/>
+      <c r="D4" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="33" t="s">
-        <v>300</v>
+        <v>388</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
@@ -5076,7 +5088,7 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="33" t="s">
-        <v>301</v>
+        <v>389</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -5088,7 +5100,7 @@
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="21" t="s">
-        <v>381</v>
+        <v>279</v>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
@@ -5105,20 +5117,20 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>382</v>
-      </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
+      <c r="D8" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="21" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
@@ -5130,7 +5142,7 @@
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="21" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
@@ -5147,20 +5159,20 @@
       <c r="C11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="24" t="s">
-        <v>383</v>
-      </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="26"/>
+      <c r="D11" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="21" t="s">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
@@ -5172,7 +5184,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="21" t="s">
-        <v>393</v>
+        <v>364</v>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
@@ -5189,20 +5201,20 @@
       <c r="C14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="24" t="s">
-        <v>384</v>
-      </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="26"/>
+      <c r="D14" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="29"/>
     </row>
     <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="21" t="s">
-        <v>394</v>
+        <v>288</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
@@ -5214,7 +5226,7 @@
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="21" t="s">
-        <v>388</v>
+        <v>284</v>
       </c>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
@@ -5226,7 +5238,7 @@
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="21" t="s">
-        <v>389</v>
+        <v>285</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
@@ -5238,34 +5250,39 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="21" t="s">
-        <v>390</v>
+        <v>286</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
       <c r="G18" s="22"/>
       <c r="H18" s="23"/>
     </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="21" t="s">
-        <v>391</v>
+        <v>287</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="22"/>
       <c r="G19" s="22"/>
       <c r="H19" s="23"/>
     </row>
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="23"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
+  <mergeCells count="20">
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="D2:H2"/>
@@ -5278,6 +5295,14 @@
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5307,25 +5332,25 @@
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="26"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
     </row>
     <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="45" t="s">
+      <c r="D8" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -5356,7 +5381,7 @@
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="33" t="s">
-        <v>176</v>
+        <v>298</v>
       </c>
       <c r="E11" s="34"/>
       <c r="F11" s="34"/>
@@ -5368,7 +5393,7 @@
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="33" t="s">
-        <v>177</v>
+        <v>299</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
@@ -5379,20 +5404,20 @@
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="38"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="45"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="9" t="s">
-        <v>395</v>
+        <v>289</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -5409,13 +5434,13 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
+      <c r="D15" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
@@ -5433,32 +5458,32 @@
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="29"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="38"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="41"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="33" t="s">
-        <v>379</v>
+        <v>300</v>
       </c>
       <c r="E19" s="34"/>
       <c r="F19" s="34"/>
@@ -5470,7 +5495,7 @@
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="33" t="s">
-        <v>380</v>
+        <v>301</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="34"/>
@@ -5482,7 +5507,7 @@
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="21" t="s">
-        <v>246</v>
+        <v>302</v>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
@@ -5499,13 +5524,13 @@
       <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="24" t="s">
-        <v>324</v>
-      </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="26"/>
+      <c r="D22" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="29"/>
     </row>
     <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
@@ -5523,32 +5548,32 @@
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="29"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="38"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="30" t="s">
+      <c r="D25" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="32"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="41"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="33" t="s">
-        <v>179</v>
+        <v>303</v>
       </c>
       <c r="E26" s="34"/>
       <c r="F26" s="34"/>
@@ -5560,7 +5585,7 @@
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="33" t="s">
-        <v>180</v>
+        <v>304</v>
       </c>
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
@@ -5577,20 +5602,20 @@
       <c r="C28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D28" s="24" t="s">
-        <v>325</v>
-      </c>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="26"/>
+      <c r="D28" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="29"/>
     </row>
     <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="21" t="s">
-        <v>253</v>
+        <v>187</v>
       </c>
       <c r="E29" s="22"/>
       <c r="F29" s="22"/>
@@ -5601,32 +5626,32 @@
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
-      <c r="D30" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="29"/>
+      <c r="D30" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="38"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="32"/>
+      <c r="D31" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="41"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="33" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="E32" s="34"/>
       <c r="F32" s="34"/>
@@ -5643,20 +5668,20 @@
       <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="24" t="s">
-        <v>327</v>
-      </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="26"/>
+      <c r="D33" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="29"/>
     </row>
     <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="21" t="s">
-        <v>328</v>
+        <v>246</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
@@ -5668,7 +5693,7 @@
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="21" t="s">
-        <v>261</v>
+        <v>193</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="22"/>
@@ -5680,7 +5705,7 @@
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="21" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
@@ -5692,7 +5717,7 @@
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="21" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="22"/>
@@ -5704,7 +5729,7 @@
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="21" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="22"/>
@@ -5721,32 +5746,32 @@
       <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D39" s="24" t="s">
-        <v>331</v>
-      </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="26"/>
+      <c r="D39" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="29"/>
     </row>
     <row r="40" spans="1:8" ht="78.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="42" t="s">
-        <v>332</v>
-      </c>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="44"/>
+      <c r="D40" s="30" t="s">
+        <v>308</v>
+      </c>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="32"/>
     </row>
     <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="21" t="s">
-        <v>333</v>
+        <v>248</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
@@ -5758,7 +5783,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="21" t="s">
-        <v>334</v>
+        <v>249</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
@@ -5775,20 +5800,20 @@
       <c r="C43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D43" s="24" t="s">
-        <v>335</v>
-      </c>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="26"/>
+      <c r="D43" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="29"/>
     </row>
     <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="21" t="s">
-        <v>319</v>
+        <v>238</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
@@ -5800,7 +5825,7 @@
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="21" t="s">
-        <v>320</v>
+        <v>239</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="22"/>
@@ -5812,7 +5837,7 @@
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="21" t="s">
-        <v>336</v>
+        <v>251</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
@@ -5824,7 +5849,7 @@
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="21" t="s">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="22"/>
@@ -5841,32 +5866,32 @@
       <c r="C48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D48" s="24" t="s">
-        <v>338</v>
-      </c>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="26"/>
+      <c r="D48" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="29"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
-      <c r="D49" s="39" t="s">
-        <v>339</v>
-      </c>
-      <c r="E49" s="40"/>
-      <c r="F49" s="40"/>
-      <c r="G49" s="40"/>
-      <c r="H49" s="41"/>
+      <c r="D49" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="26"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="33" t="s">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="E50" s="34"/>
       <c r="F50" s="34"/>
@@ -5877,25 +5902,25 @@
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="39" t="s">
-        <v>341</v>
-      </c>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="41"/>
+      <c r="D51" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="26"/>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="39" t="s">
-        <v>342</v>
-      </c>
-      <c r="E52" s="40"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="41"/>
+      <c r="D52" s="24" t="s">
+        <v>311</v>
+      </c>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="26"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
@@ -5907,20 +5932,20 @@
       <c r="C53" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="24" t="s">
-        <v>343</v>
-      </c>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="25"/>
-      <c r="H53" s="26"/>
+      <c r="D53" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="29"/>
     </row>
     <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="21" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="22"/>
@@ -5932,7 +5957,7 @@
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="21" t="s">
-        <v>345</v>
+        <v>256</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="22"/>
@@ -5949,20 +5974,20 @@
       <c r="C56" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D56" s="24" t="s">
-        <v>346</v>
-      </c>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="26"/>
+      <c r="D56" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="29"/>
     </row>
     <row r="57" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="21" t="s">
-        <v>347</v>
+        <v>258</v>
       </c>
       <c r="E57" s="22"/>
       <c r="F57" s="22"/>
@@ -5974,7 +5999,7 @@
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="21" t="s">
-        <v>348</v>
+        <v>259</v>
       </c>
       <c r="E58" s="22"/>
       <c r="F58" s="22"/>
@@ -5986,7 +6011,7 @@
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="21" t="s">
-        <v>349</v>
+        <v>260</v>
       </c>
       <c r="E59" s="22"/>
       <c r="F59" s="22"/>
@@ -5998,7 +6023,7 @@
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="21" t="s">
-        <v>350</v>
+        <v>261</v>
       </c>
       <c r="E60" s="22"/>
       <c r="F60" s="22"/>
@@ -6010,7 +6035,7 @@
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="21" t="s">
-        <v>351</v>
+        <v>262</v>
       </c>
       <c r="E61" s="22"/>
       <c r="F61" s="22"/>
@@ -6019,36 +6044,12 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="D61:H61"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D56:H56"/>
-    <mergeCell ref="D57:H57"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
     <mergeCell ref="D21:H21"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D34:H34"/>
@@ -6065,12 +6066,36 @@
     <mergeCell ref="D30:H30"/>
     <mergeCell ref="D31:H31"/>
     <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="D61:H61"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D56:H56"/>
+    <mergeCell ref="D57:H57"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6105,25 +6130,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -6141,49 +6166,49 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="38"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="45"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
+      <c r="D5" s="43" t="s">
+        <v>313</v>
+      </c>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="38"/>
+      <c r="D6" s="43" t="s">
+        <v>314</v>
+      </c>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="45"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -6195,13 +6220,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -6219,32 +6244,32 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="29"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="38"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="33" t="s">
-        <v>183</v>
+        <v>315</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
@@ -6256,7 +6281,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="33" t="s">
-        <v>184</v>
+        <v>316</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
@@ -6268,7 +6293,7 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="21" t="s">
-        <v>49</v>
+        <v>317</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
@@ -6285,13 +6310,13 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
@@ -6322,7 +6347,7 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="21" t="s">
-        <v>185</v>
+        <v>318</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -6351,25 +6376,25 @@
       <c r="C20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="26"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="29"/>
     </row>
     <row r="21" spans="1:8" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="41"/>
+      <c r="D21" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="26"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -6381,20 +6406,20 @@
       <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="26"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="29"/>
     </row>
     <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="21" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="22"/>
@@ -6406,7 +6431,7 @@
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="21" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -6418,7 +6443,7 @@
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="21" t="s">
-        <v>352</v>
+        <v>263</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="22"/>
@@ -6435,20 +6460,20 @@
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="26"/>
+      <c r="D26" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="29"/>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="21" t="s">
-        <v>354</v>
+        <v>265</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
@@ -6460,7 +6485,7 @@
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="21" t="s">
-        <v>355</v>
+        <v>266</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -6477,20 +6502,20 @@
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="24" t="s">
-        <v>356</v>
-      </c>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="26"/>
+      <c r="D29" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="29"/>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="21" t="s">
-        <v>357</v>
+        <v>268</v>
       </c>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -6502,7 +6527,7 @@
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="21" t="s">
-        <v>267</v>
+        <v>198</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="22"/>
@@ -6514,7 +6539,7 @@
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="21" t="s">
-        <v>358</v>
+        <v>269</v>
       </c>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -6526,7 +6551,7 @@
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="21" t="s">
-        <v>359</v>
+        <v>270</v>
       </c>
       <c r="E33" s="22"/>
       <c r="F33" s="22"/>
@@ -6538,7 +6563,7 @@
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="21" t="s">
-        <v>360</v>
+        <v>271</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
@@ -6547,15 +6572,18 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="D14:H14"/>
     <mergeCell ref="D15:H15"/>
@@ -6568,18 +6596,15 @@
     <mergeCell ref="D22:H22"/>
     <mergeCell ref="D23:H23"/>
     <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
   </mergeCells>
   <pageMargins left="0.70866141732283461" right="0.70866141732283461" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6610,25 +6635,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -6659,7 +6684,7 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="33" t="s">
-        <v>216</v>
+        <v>290</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
@@ -6671,7 +6696,7 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="33" t="s">
-        <v>217</v>
+        <v>291</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -6682,20 +6707,20 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="9" t="s">
-        <v>395</v>
+        <v>289</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -6712,13 +6737,13 @@
       <c r="C9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="29"/>
     </row>
     <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
@@ -6736,32 +6761,32 @@
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="29"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="38"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="32"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="41"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="33" t="s">
-        <v>364</v>
+        <v>292</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
@@ -6773,7 +6798,7 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="33" t="s">
-        <v>365</v>
+        <v>293</v>
       </c>
       <c r="E14" s="34"/>
       <c r="F14" s="34"/>
@@ -6785,7 +6810,7 @@
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="21" t="s">
-        <v>246</v>
+        <v>182</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
@@ -6802,20 +6827,20 @@
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="26"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="21" t="s">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
@@ -6827,7 +6852,7 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="21" t="s">
-        <v>241</v>
+        <v>181</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -6839,7 +6864,7 @@
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="21" t="s">
-        <v>361</v>
+        <v>294</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="22"/>
@@ -6851,7 +6876,7 @@
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="21" t="s">
-        <v>362</v>
+        <v>295</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
@@ -6863,7 +6888,7 @@
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="21" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
@@ -6880,32 +6905,32 @@
       <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="26"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="29"/>
     </row>
     <row r="23" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="42" t="s">
-        <v>363</v>
-      </c>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="44"/>
+      <c r="D23" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="32"/>
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="21" t="s">
-        <v>239</v>
+        <v>179</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -6917,7 +6942,7 @@
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="21" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="22"/>
@@ -6934,20 +6959,20 @@
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="26"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="29"/>
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="21" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
@@ -6959,7 +6984,7 @@
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="21" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -6971,7 +6996,7 @@
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="21" t="s">
-        <v>352</v>
+        <v>263</v>
       </c>
       <c r="E29" s="22"/>
       <c r="F29" s="22"/>
@@ -6988,32 +7013,32 @@
       <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="26"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="29"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="39" t="s">
+      <c r="D31" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="41"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="26"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="33" t="s">
-        <v>218</v>
+        <v>296</v>
       </c>
       <c r="E32" s="34"/>
       <c r="F32" s="34"/>
@@ -7024,25 +7049,25 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="D33" s="39" t="s">
+      <c r="D33" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="40"/>
-      <c r="H33" s="41"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="26"/>
     </row>
     <row r="34" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="39" t="s">
+      <c r="D34" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="41"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="26"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
@@ -7054,13 +7079,13 @@
       <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="24" t="s">
+      <c r="D35" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="26"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="29"/>
     </row>
     <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
@@ -7096,20 +7121,20 @@
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D38" s="24" t="s">
+      <c r="D38" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="26"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="29"/>
     </row>
     <row r="39" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="21" t="s">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="E39" s="22"/>
       <c r="F39" s="22"/>
@@ -7121,7 +7146,7 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="21" t="s">
-        <v>232</v>
+        <v>173</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
@@ -7133,7 +7158,7 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="21" t="s">
-        <v>271</v>
+        <v>202</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
@@ -7145,7 +7170,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="21" t="s">
-        <v>272</v>
+        <v>203</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
@@ -7157,7 +7182,7 @@
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="21" t="s">
-        <v>273</v>
+        <v>204</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="22"/>
@@ -7166,16 +7191,24 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D22:H22"/>
     <mergeCell ref="D23:H23"/>
@@ -7188,24 +7221,16 @@
     <mergeCell ref="D30:H30"/>
     <mergeCell ref="D31:H31"/>
     <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7236,25 +7261,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -7285,7 +7310,7 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="33" t="s">
-        <v>219</v>
+        <v>320</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
@@ -7297,7 +7322,7 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="33" t="s">
-        <v>220</v>
+        <v>321</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -7308,13 +7333,13 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -7326,13 +7351,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -7350,32 +7375,32 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="29"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="38"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="33" t="s">
-        <v>366</v>
+        <v>322</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
@@ -7387,7 +7412,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="33" t="s">
-        <v>367</v>
+        <v>323</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
@@ -7399,7 +7424,7 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="21" t="s">
-        <v>246</v>
+        <v>182</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
@@ -7416,20 +7441,20 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="21" t="s">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
@@ -7441,7 +7466,7 @@
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="21" t="s">
-        <v>241</v>
+        <v>181</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
@@ -7453,7 +7478,7 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="21" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -7465,7 +7490,7 @@
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="21" t="s">
-        <v>369</v>
+        <v>325</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="22"/>
@@ -7477,7 +7502,7 @@
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="21" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
@@ -7494,80 +7519,80 @@
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="26"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="29"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="42" t="s">
-        <v>370</v>
-      </c>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="44"/>
+      <c r="D22" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="44"/>
+      <c r="D23" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="32"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="44"/>
+      <c r="D24" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="32"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="42" t="s">
-        <v>223</v>
-      </c>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="44"/>
+      <c r="D25" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="32"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="44"/>
+      <c r="D26" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="32"/>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="21" t="s">
-        <v>239</v>
+        <v>179</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
@@ -7579,7 +7604,7 @@
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="21" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -7596,20 +7621,20 @@
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="24" t="s">
+      <c r="D29" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="26"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="29"/>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="21" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -7621,7 +7646,7 @@
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="21" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="22"/>
@@ -7633,7 +7658,7 @@
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="21" t="s">
-        <v>352</v>
+        <v>263</v>
       </c>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -7650,32 +7675,32 @@
       <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="26"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="29"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="39" t="s">
+      <c r="D34" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="41"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="26"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="33" t="s">
-        <v>225</v>
+        <v>330</v>
       </c>
       <c r="E35" s="34"/>
       <c r="F35" s="34"/>
@@ -7686,25 +7711,25 @@
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
-      <c r="D36" s="39" t="s">
+      <c r="D36" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-      <c r="G36" s="40"/>
-      <c r="H36" s="41"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="26"/>
     </row>
     <row r="37" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="39" t="s">
+      <c r="D37" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="41"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="26"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
@@ -7716,13 +7741,13 @@
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D38" s="24" t="s">
+      <c r="D38" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="26"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="29"/>
     </row>
     <row r="39" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
@@ -7758,20 +7783,20 @@
       <c r="C41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D41" s="24" t="s">
+      <c r="D41" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="26"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="29"/>
     </row>
     <row r="42" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="21" t="s">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
@@ -7783,7 +7808,7 @@
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="21" t="s">
-        <v>232</v>
+        <v>173</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="22"/>
@@ -7795,7 +7820,7 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="21" t="s">
-        <v>271</v>
+        <v>202</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
@@ -7807,7 +7832,7 @@
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="21" t="s">
-        <v>272</v>
+        <v>203</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="22"/>
@@ -7819,7 +7844,7 @@
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="21" t="s">
-        <v>273</v>
+        <v>204</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
@@ -7828,6 +7853,34 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
     <mergeCell ref="D35:H35"/>
     <mergeCell ref="D36:H36"/>
     <mergeCell ref="D21:H21"/>
@@ -7844,34 +7897,6 @@
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7902,25 +7927,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -7951,7 +7976,7 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="33" t="s">
-        <v>187</v>
+        <v>331</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
@@ -7963,7 +7988,7 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="33" t="s">
-        <v>188</v>
+        <v>332</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -7974,13 +7999,13 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -7992,13 +8017,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
+      <c r="D8" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -8016,32 +8041,32 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="29"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="38"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="33" t="s">
-        <v>189</v>
+        <v>333</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
@@ -8053,7 +8078,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="33" t="s">
-        <v>190</v>
+        <v>334</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
@@ -8082,13 +8107,13 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
+      <c r="D15" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
@@ -8106,32 +8131,32 @@
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="29"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="38"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="41"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="33" t="s">
-        <v>192</v>
+        <v>333</v>
       </c>
       <c r="E19" s="34"/>
       <c r="F19" s="34"/>
@@ -8143,7 +8168,7 @@
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="33" t="s">
-        <v>193</v>
+        <v>334</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="34"/>
@@ -8172,13 +8197,13 @@
       <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="24" t="s">
-        <v>371</v>
-      </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="26"/>
+      <c r="D22" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="29"/>
     </row>
     <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
@@ -8209,7 +8234,7 @@
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="21" t="s">
-        <v>194</v>
+        <v>335</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="22"/>
@@ -8221,7 +8246,7 @@
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="21" t="s">
-        <v>195</v>
+        <v>336</v>
       </c>
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
@@ -8250,25 +8275,25 @@
       <c r="C28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D28" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="26"/>
+      <c r="D28" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="29"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
-      <c r="D29" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="44"/>
+      <c r="D29" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="32"/>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
@@ -8298,23 +8323,25 @@
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="48"/>
+      <c r="D32" s="49" t="s">
+        <v>337</v>
+      </c>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="51"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="18" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
+      <c r="F33" s="19" t="s">
+        <v>339</v>
+      </c>
       <c r="G33" s="19"/>
       <c r="H33" s="20"/>
     </row>
@@ -8322,25 +8349,25 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="51"/>
+      <c r="D34" s="52" t="s">
+        <v>338</v>
+      </c>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="54"/>
     </row>
     <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="52" t="s">
-        <v>199</v>
-      </c>
-      <c r="E35" s="53"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="54"/>
+      <c r="D35" s="55" t="s">
+        <v>340</v>
+      </c>
+      <c r="E35" s="56"/>
+      <c r="F35" s="56"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="57"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
@@ -8352,32 +8379,32 @@
       <c r="C36" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="26"/>
+      <c r="D36" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="29"/>
     </row>
     <row r="37" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="39" t="s">
+      <c r="D37" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="41"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="26"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="15" t="s">
-        <v>201</v>
+        <v>342</v>
       </c>
       <c r="E38" s="16"/>
       <c r="F38" s="16"/>
@@ -8401,7 +8428,7 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="21" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
@@ -8418,32 +8445,32 @@
       <c r="C41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D41" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="26"/>
+      <c r="D41" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="E41" s="28"/>
+      <c r="F41" s="28"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="29"/>
     </row>
     <row r="42" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="39" t="s">
-        <v>372</v>
-      </c>
-      <c r="E42" s="40"/>
-      <c r="F42" s="40"/>
-      <c r="G42" s="40"/>
-      <c r="H42" s="41"/>
+      <c r="D42" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="26"/>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="15" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="E43" s="16"/>
       <c r="F43" s="16"/>
@@ -8454,25 +8481,25 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="39" t="s">
-        <v>374</v>
-      </c>
-      <c r="E44" s="40"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="41"/>
+      <c r="D44" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="26"/>
     </row>
     <row r="45" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
-      <c r="D45" s="39" t="s">
-        <v>375</v>
-      </c>
-      <c r="E45" s="40"/>
-      <c r="F45" s="40"/>
-      <c r="G45" s="40"/>
-      <c r="H45" s="41"/>
+      <c r="D45" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="E45" s="25"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="26"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -8484,37 +8511,37 @@
       <c r="C46" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D46" s="24" t="s">
-        <v>376</v>
-      </c>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="26"/>
+      <c r="D46" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="29"/>
     </row>
     <row r="47" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="E47" s="40"/>
-      <c r="F47" s="40"/>
-      <c r="G47" s="40"/>
-      <c r="H47" s="41"/>
+      <c r="D47" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="26"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
-      <c r="D48" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="E48" s="40"/>
-      <c r="F48" s="40"/>
-      <c r="G48" s="40"/>
-      <c r="H48" s="41"/>
+      <c r="D48" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="26"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
@@ -8526,61 +8553,61 @@
       <c r="C49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D49" s="55" t="s">
-        <v>377</v>
-      </c>
-      <c r="E49" s="56"/>
-      <c r="F49" s="56"/>
-      <c r="G49" s="56"/>
-      <c r="H49" s="57"/>
+      <c r="D49" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="48"/>
     </row>
     <row r="50" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="39" t="s">
+      <c r="D50" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="41"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="26"/>
     </row>
     <row r="51" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="39" t="s">
+      <c r="D51" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="41"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="26"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="39" t="s">
+      <c r="D52" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E52" s="40"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="40"/>
-      <c r="H52" s="41"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="26"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="39" t="s">
+      <c r="D53" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="E53" s="40"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="40"/>
-      <c r="H53" s="41"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="26"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
@@ -8596,39 +8623,6 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
     <mergeCell ref="D27:H27"/>
     <mergeCell ref="D26:H26"/>
     <mergeCell ref="D8:H8"/>
@@ -8645,6 +8639,39 @@
     <mergeCell ref="D14:H14"/>
     <mergeCell ref="D22:H22"/>
     <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D49:H49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8675,25 +8702,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -8724,7 +8751,7 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="33" t="s">
-        <v>202</v>
+        <v>343</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
@@ -8736,7 +8763,7 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="33" t="s">
-        <v>203</v>
+        <v>344</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -8747,13 +8774,13 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -8765,13 +8792,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -8789,32 +8816,32 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="29"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="38"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="33" t="s">
-        <v>244</v>
+        <v>345</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
@@ -8826,7 +8853,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="33" t="s">
-        <v>245</v>
+        <v>346</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
@@ -8838,7 +8865,7 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="21" t="s">
-        <v>246</v>
+        <v>182</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
@@ -8855,20 +8882,20 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="26"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="21" t="s">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="E16" s="22"/>
       <c r="F16" s="22"/>
@@ -8880,7 +8907,7 @@
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="21" t="s">
-        <v>241</v>
+        <v>181</v>
       </c>
       <c r="E17" s="22"/>
       <c r="F17" s="22"/>
@@ -8892,7 +8919,7 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="21" t="s">
-        <v>242</v>
+        <v>347</v>
       </c>
       <c r="E18" s="22"/>
       <c r="F18" s="22"/>
@@ -8904,7 +8931,7 @@
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="21" t="s">
-        <v>243</v>
+        <v>348</v>
       </c>
       <c r="E19" s="22"/>
       <c r="F19" s="22"/>
@@ -8916,7 +8943,7 @@
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="21" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
@@ -8933,32 +8960,32 @@
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="26"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="29"/>
     </row>
     <row r="22" spans="1:8" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="44"/>
+      <c r="D22" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="21" t="s">
-        <v>239</v>
+        <v>179</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="22"/>
@@ -8970,7 +8997,7 @@
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="21" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E24" s="22"/>
       <c r="F24" s="22"/>
@@ -8987,20 +9014,20 @@
       <c r="C25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="26"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="29"/>
     </row>
     <row r="26" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="21" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
@@ -9012,7 +9039,7 @@
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="21" t="s">
-        <v>237</v>
+        <v>178</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
@@ -9024,7 +9051,7 @@
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="21" t="s">
-        <v>235</v>
+        <v>176</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -9036,7 +9063,7 @@
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="21" t="s">
-        <v>236</v>
+        <v>177</v>
       </c>
       <c r="E29" s="22"/>
       <c r="F29" s="22"/>
@@ -9053,13 +9080,13 @@
       <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="26"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="29"/>
     </row>
     <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
@@ -9078,7 +9105,7 @@
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="21" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -9102,7 +9129,7 @@
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="21" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
@@ -9119,13 +9146,13 @@
       <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="24" t="s">
+      <c r="D35" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="26"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="29"/>
     </row>
     <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
@@ -9161,20 +9188,20 @@
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D38" s="24" t="s">
+      <c r="D38" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="26"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="29"/>
     </row>
     <row r="39" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="21" t="s">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="E39" s="22"/>
       <c r="F39" s="22"/>
@@ -9186,7 +9213,7 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="21" t="s">
-        <v>232</v>
+        <v>173</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
@@ -9198,7 +9225,7 @@
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="21" t="s">
-        <v>231</v>
+        <v>172</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
@@ -9210,7 +9237,7 @@
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="21" t="s">
-        <v>233</v>
+        <v>174</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
@@ -9222,7 +9249,7 @@
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="21" t="s">
-        <v>234</v>
+        <v>175</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="22"/>
@@ -9231,15 +9258,24 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
     <mergeCell ref="D34:H34"/>
     <mergeCell ref="D21:H21"/>
     <mergeCell ref="D22:H22"/>
@@ -9254,24 +9290,15 @@
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D27:H27"/>
     <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9280,7 +9307,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BE7E8A1-AE48-44F4-AC4E-BA56D53EEA65}">
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -9300,25 +9327,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -9349,7 +9376,7 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="33" t="s">
-        <v>65</v>
+        <v>343</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
@@ -9361,7 +9388,7 @@
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="33" t="s">
-        <v>66</v>
+        <v>291</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
@@ -9372,13 +9399,13 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="36" t="s">
+      <c r="D7" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -9390,13 +9417,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="26"/>
+      <c r="D8" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -9414,32 +9441,32 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="29"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="38"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="41"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="33" t="s">
-        <v>247</v>
+        <v>322</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
@@ -9451,7 +9478,7 @@
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="33" t="s">
-        <v>248</v>
+        <v>293</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
@@ -9463,7 +9490,7 @@
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="33" t="s">
-        <v>249</v>
+        <v>183</v>
       </c>
       <c r="E14" s="34"/>
       <c r="F14" s="34"/>
@@ -9475,7 +9502,7 @@
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="21" t="s">
-        <v>250</v>
+        <v>184</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
@@ -9492,13 +9519,13 @@
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="26"/>
+      <c r="D16" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
@@ -9516,32 +9543,32 @@
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="38"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="32"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="33" t="s">
-        <v>67</v>
+        <v>351</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="34"/>
@@ -9553,7 +9580,7 @@
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="33" t="s">
-        <v>68</v>
+        <v>352</v>
       </c>
       <c r="E21" s="34"/>
       <c r="F21" s="34"/>
@@ -9565,7 +9592,7 @@
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="33" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="E22" s="34"/>
       <c r="F22" s="34"/>
@@ -9577,7 +9604,7 @@
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="21" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="22"/>
@@ -9594,20 +9621,20 @@
       <c r="C24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="26"/>
+      <c r="D24" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="29"/>
     </row>
     <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="21" t="s">
-        <v>253</v>
+        <v>187</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="22"/>
@@ -9618,32 +9645,32 @@
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
+      <c r="D26" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="38"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="32"/>
+      <c r="D27" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="33" t="s">
-        <v>256</v>
+        <v>353</v>
       </c>
       <c r="E28" s="34"/>
       <c r="F28" s="34"/>
@@ -9655,7 +9682,7 @@
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="33" t="s">
-        <v>257</v>
+        <v>354</v>
       </c>
       <c r="E29" s="34"/>
       <c r="F29" s="34"/>
@@ -9667,7 +9694,7 @@
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="21" t="s">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -9684,20 +9711,20 @@
       <c r="C31" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D31" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="26"/>
+      <c r="D31" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="29"/>
     </row>
     <row r="32" spans="1:8" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="21" t="s">
-        <v>260</v>
+        <v>192</v>
       </c>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -9709,7 +9736,7 @@
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="21" t="s">
-        <v>261</v>
+        <v>193</v>
       </c>
       <c r="E33" s="22"/>
       <c r="F33" s="22"/>
@@ -9721,7 +9748,7 @@
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="21" t="s">
-        <v>262</v>
+        <v>355</v>
       </c>
       <c r="E34" s="22"/>
       <c r="F34" s="22"/>
@@ -9733,7 +9760,7 @@
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="21" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="22"/>
@@ -9750,13 +9777,13 @@
       <c r="C36" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="26"/>
+      <c r="D36" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="29"/>
     </row>
     <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
@@ -9786,32 +9813,32 @@
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="E39" s="40"/>
-      <c r="F39" s="40"/>
-      <c r="G39" s="40"/>
-      <c r="H39" s="41"/>
+      <c r="D39" s="24" t="s">
+        <v>356</v>
+      </c>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="26"/>
     </row>
     <row r="40" spans="1:8" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="39" t="s">
-        <v>161</v>
-      </c>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="41"/>
+      <c r="D40" s="24" t="s">
+        <v>357</v>
+      </c>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="26"/>
     </row>
     <row r="41" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="21" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
@@ -9828,20 +9855,20 @@
       <c r="C42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D42" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="26"/>
+      <c r="D42" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="29"/>
     </row>
     <row r="43" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="21" t="s">
-        <v>266</v>
+        <v>197</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="22"/>
@@ -9853,7 +9880,7 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="21" t="s">
-        <v>267</v>
+        <v>198</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
@@ -9865,7 +9892,7 @@
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="21" t="s">
-        <v>268</v>
+        <v>199</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="22"/>
@@ -9877,7 +9904,7 @@
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="21" t="s">
-        <v>269</v>
+        <v>200</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
@@ -9889,7 +9916,7 @@
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="21" t="s">
-        <v>270</v>
+        <v>201</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="22"/>
@@ -9906,76 +9933,116 @@
       <c r="C48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D48" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="26"/>
-    </row>
-    <row r="49" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D48" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="29"/>
+    </row>
+    <row r="49" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="21" t="s">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="22"/>
       <c r="G49" s="22"/>
       <c r="H49" s="23"/>
     </row>
-    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="21" t="s">
-        <v>232</v>
+        <v>173</v>
       </c>
       <c r="E50" s="22"/>
       <c r="F50" s="22"/>
       <c r="G50" s="22"/>
       <c r="H50" s="23"/>
     </row>
-    <row r="51" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="21" t="s">
-        <v>271</v>
+        <v>202</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="22"/>
       <c r="G51" s="22"/>
       <c r="H51" s="23"/>
     </row>
-    <row r="52" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="21" t="s">
-        <v>272</v>
+        <v>203</v>
       </c>
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
       <c r="G52" s="22"/>
       <c r="H52" s="23"/>
     </row>
-    <row r="53" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="21" t="s">
-        <v>273</v>
+        <v>204</v>
       </c>
       <c r="E53" s="22"/>
       <c r="F53" s="22"/>
       <c r="G53" s="22"/>
       <c r="H53" s="23"/>
     </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J60" t="s">
+        <v>358</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
     <mergeCell ref="D53:H53"/>
     <mergeCell ref="D14:H14"/>
     <mergeCell ref="D22:H22"/>
@@ -9992,41 +10059,6 @@
     <mergeCell ref="D24:H24"/>
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10054,13 +10086,13 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="26"/>
+      <c r="D1" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
@@ -10090,13 +10122,13 @@
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
-      <c r="D4" s="36" t="s">
-        <v>274</v>
-      </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="38"/>
+      <c r="D4" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="45"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -10108,20 +10140,20 @@
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="26"/>
+      <c r="D5" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="29"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
       <c r="D6" s="21" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
@@ -10133,7 +10165,7 @@
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
       <c r="D7" s="21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
@@ -10145,7 +10177,7 @@
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
       <c r="D8" s="21" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
@@ -10157,7 +10189,7 @@
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
       <c r="D9" s="21" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
@@ -10169,7 +10201,7 @@
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
       <c r="D10" s="21" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
@@ -10181,7 +10213,7 @@
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
       <c r="D11" s="21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
@@ -10193,7 +10225,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
       <c r="D12" s="21" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
@@ -10205,7 +10237,7 @@
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
       <c r="D13" s="21" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E13" s="22"/>
       <c r="F13" s="22"/>
@@ -10217,7 +10249,7 @@
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
       <c r="D14" s="21" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
@@ -10229,7 +10261,7 @@
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
       <c r="D15" s="21" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="22"/>
@@ -10246,13 +10278,13 @@
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="26"/>
+      <c r="D16" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="29"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
@@ -10270,25 +10302,25 @@
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="38"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="32"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="12"/>
@@ -10299,12 +10331,8 @@
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>84</v>
-      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
@@ -10315,19 +10343,15 @@
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
-      <c r="G21" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>86</v>
-      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="11"/>
     </row>
     <row r="22" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="21" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E22" s="22"/>
       <c r="F22" s="22"/>
@@ -10344,32 +10368,32 @@
       <c r="C23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="26"/>
+      <c r="D23" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="29"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="42" t="s">
-        <v>275</v>
-      </c>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="44"/>
+      <c r="D24" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="32"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="21" t="s">
-        <v>276</v>
+        <v>207</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="22"/>
@@ -10381,7 +10405,7 @@
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="21" t="s">
-        <v>277</v>
+        <v>208</v>
       </c>
       <c r="E26" s="22"/>
       <c r="F26" s="22"/>
@@ -10393,7 +10417,7 @@
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="21" t="s">
-        <v>278</v>
+        <v>209</v>
       </c>
       <c r="E27" s="22"/>
       <c r="F27" s="22"/>
@@ -10405,7 +10429,7 @@
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="21" t="s">
-        <v>278</v>
+        <v>209</v>
       </c>
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
@@ -10422,20 +10446,20 @@
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="26"/>
+      <c r="D29" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="29"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="21" t="s">
-        <v>279</v>
+        <v>210</v>
       </c>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -10447,7 +10471,7 @@
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
       <c r="D31" s="21" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E31" s="22"/>
       <c r="F31" s="22"/>
@@ -10459,7 +10483,7 @@
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
       <c r="D32" s="21" t="s">
-        <v>280</v>
+        <v>211</v>
       </c>
       <c r="E32" s="22"/>
       <c r="F32" s="22"/>
@@ -10471,7 +10495,7 @@
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="21" t="s">
-        <v>281</v>
+        <v>212</v>
       </c>
       <c r="E33" s="22"/>
       <c r="F33" s="22"/>
@@ -10488,20 +10512,20 @@
       <c r="C34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="26"/>
+      <c r="D34" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="29"/>
     </row>
     <row r="35" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
       <c r="D35" s="21" t="s">
-        <v>282</v>
+        <v>213</v>
       </c>
       <c r="E35" s="22"/>
       <c r="F35" s="22"/>
@@ -10513,7 +10537,7 @@
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="21" t="s">
-        <v>283</v>
+        <v>214</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
@@ -10525,7 +10549,7 @@
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="21" t="s">
-        <v>284</v>
+        <v>215</v>
       </c>
       <c r="E37" s="22"/>
       <c r="F37" s="22"/>
@@ -10537,7 +10561,7 @@
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
       <c r="D38" s="21" t="s">
-        <v>285</v>
+        <v>216</v>
       </c>
       <c r="E38" s="22"/>
       <c r="F38" s="22"/>
@@ -10554,20 +10578,20 @@
       <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D39" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="26"/>
+      <c r="D39" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="29"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
       <c r="D40" s="21" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
@@ -10579,7 +10603,7 @@
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
       <c r="D41" s="21" t="s">
-        <v>287</v>
+        <v>218</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
@@ -10591,7 +10615,7 @@
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="21" t="s">
-        <v>288</v>
+        <v>219</v>
       </c>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
@@ -10603,7 +10627,7 @@
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
       <c r="D43" s="21" t="s">
-        <v>289</v>
+        <v>220</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="22"/>
@@ -10615,7 +10639,7 @@
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
       <c r="D44" s="21" t="s">
-        <v>290</v>
+        <v>221</v>
       </c>
       <c r="E44" s="22"/>
       <c r="F44" s="22"/>
@@ -10627,7 +10651,7 @@
       <c r="B45" s="12"/>
       <c r="C45" s="12"/>
       <c r="D45" s="21" t="s">
-        <v>291</v>
+        <v>222</v>
       </c>
       <c r="E45" s="22"/>
       <c r="F45" s="22"/>
@@ -10639,7 +10663,7 @@
       <c r="B46" s="12"/>
       <c r="C46" s="12"/>
       <c r="D46" s="21" t="s">
-        <v>292</v>
+        <v>223</v>
       </c>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
@@ -10651,7 +10675,7 @@
       <c r="B47" s="12"/>
       <c r="C47" s="12"/>
       <c r="D47" s="21" t="s">
-        <v>293</v>
+        <v>224</v>
       </c>
       <c r="E47" s="22"/>
       <c r="F47" s="22"/>
@@ -10663,7 +10687,7 @@
       <c r="B48" s="12"/>
       <c r="C48" s="12"/>
       <c r="D48" s="21" t="s">
-        <v>294</v>
+        <v>225</v>
       </c>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
@@ -10675,7 +10699,7 @@
       <c r="B49" s="12"/>
       <c r="C49" s="12"/>
       <c r="D49" s="21" t="s">
-        <v>295</v>
+        <v>226</v>
       </c>
       <c r="E49" s="22"/>
       <c r="F49" s="22"/>
@@ -10692,20 +10716,20 @@
       <c r="C50" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D50" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
-      <c r="H50" s="26"/>
+      <c r="D50" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="29"/>
     </row>
     <row r="51" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
       <c r="D51" s="21" t="s">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="E51" s="22"/>
       <c r="F51" s="22"/>
@@ -10717,7 +10741,7 @@
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
       <c r="D52" s="21" t="s">
-        <v>232</v>
+        <v>173</v>
       </c>
       <c r="E52" s="22"/>
       <c r="F52" s="22"/>
@@ -10729,7 +10753,7 @@
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
       <c r="D53" s="21" t="s">
-        <v>231</v>
+        <v>172</v>
       </c>
       <c r="E53" s="22"/>
       <c r="F53" s="22"/>
@@ -10741,7 +10765,7 @@
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
       <c r="D54" s="21" t="s">
-        <v>233</v>
+        <v>174</v>
       </c>
       <c r="E54" s="22"/>
       <c r="F54" s="22"/>
@@ -10753,7 +10777,7 @@
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
       <c r="D55" s="21" t="s">
-        <v>296</v>
+        <v>227</v>
       </c>
       <c r="E55" s="22"/>
       <c r="F55" s="22"/>
@@ -10762,16 +10786,36 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
     <mergeCell ref="D45:H45"/>
     <mergeCell ref="D34:H34"/>
     <mergeCell ref="D35:H35"/>
@@ -10784,36 +10828,16 @@
     <mergeCell ref="D42:H42"/>
     <mergeCell ref="D43:H43"/>
     <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D51:H51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Plantilla-modelo.xlsx
+++ b/Plantilla-modelo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\desarrollo-software\reporte-obras-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599AEAED-BD85-406F-BA53-4258366C8D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3F1B06-91AD-4EED-A0CE-FCA62D454841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="947" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1443,7 +1443,7 @@
     <t xml:space="preserve">2.2  Comprobar bomba grupo presión 2:          </t>
   </si>
   <si>
-    <t>4.5 Verificar seguridades (FOTOS del cuadro antes y después) prueba</t>
+    <t>4.5 Verificar seguridades (FOTOS del cuadro antes y después) prueba nueva</t>
   </si>
 </sst>
 </file>
@@ -1648,15 +1648,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1665,24 +1656,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1702,20 +1675,38 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1743,6 +1734,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -2110,25 +2110,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -2158,13 +2158,13 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="45"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -2176,13 +2176,13 @@
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="29"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="26"/>
     </row>
     <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
@@ -2200,25 +2200,25 @@
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="29"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="41"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="32"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
@@ -2270,13 +2270,13 @@
       <c r="C13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="29"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="26"/>
     </row>
     <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
@@ -2294,25 +2294,25 @@
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="38"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="41"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="32"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
@@ -2364,13 +2364,13 @@
       <c r="C20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="26"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
@@ -2442,25 +2442,25 @@
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="26"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="32"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="44"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
@@ -2496,13 +2496,13 @@
       <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="29"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="26"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
@@ -2532,25 +2532,25 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="D33" s="43" t="s">
+      <c r="D33" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="45"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="38"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="14"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="39" t="s">
         <v>242</v>
       </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="26"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="41"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
@@ -2562,13 +2562,13 @@
       <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="27" t="s">
+      <c r="D35" s="24" t="s">
         <v>237</v>
       </c>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="29"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="26"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
@@ -2610,13 +2610,13 @@
       <c r="A39" s="13"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="24" t="s">
+      <c r="D39" s="39" t="s">
         <v>241</v>
       </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="26"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="41"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
@@ -2628,13 +2628,13 @@
       <c r="C40" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="27" t="s">
+      <c r="D40" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="29"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="26"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
@@ -2670,25 +2670,25 @@
       <c r="C43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="29"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="26"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="36" t="s">
+      <c r="D44" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="38"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="29"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
@@ -2769,6 +2769,32 @@
     <row r="282" ht="45" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D16:H16"/>
@@ -2785,32 +2811,6 @@
     <mergeCell ref="D26:H26"/>
     <mergeCell ref="D27:H27"/>
     <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D43:H43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2838,13 +2838,13 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
@@ -2862,25 +2862,25 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="38"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="29"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="41"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="32"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
@@ -2928,13 +2928,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="24" t="s">
         <v>280</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -2970,13 +2970,13 @@
       <c r="C11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="24" t="s">
         <v>281</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="29"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="26"/>
     </row>
     <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
@@ -3012,13 +3012,13 @@
       <c r="C14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="29"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="26"/>
     </row>
     <row r="15" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
@@ -3082,13 +3082,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="D8:H8"/>
@@ -3101,6 +3094,13 @@
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3131,25 +3131,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -3167,49 +3167,49 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="45"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="45"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="36" t="s">
         <v>366</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="38"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="45"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -3221,13 +3221,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -3245,25 +3245,25 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="38"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="41"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
@@ -3311,13 +3311,13 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
     </row>
     <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
@@ -3389,97 +3389,97 @@
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="26"/>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="39" t="s">
         <v>371</v>
       </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="26"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="41"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="12"/>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="26"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="39" t="s">
         <v>374</v>
       </c>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="26"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="41"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="12"/>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="39" t="s">
         <v>375</v>
       </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="26"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="41"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="12"/>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="39" t="s">
         <v>373</v>
       </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="26"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="41"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="12"/>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="39" t="s">
         <v>372</v>
       </c>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="26"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="12"/>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="39" t="s">
         <v>231</v>
       </c>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="26"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="41"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -3491,13 +3491,13 @@
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="27" t="s">
+      <c r="D29" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="26"/>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
@@ -3515,13 +3515,13 @@
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="39" t="s">
         <v>376</v>
       </c>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="26"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="41"/>
     </row>
     <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
@@ -3557,13 +3557,13 @@
       <c r="C34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="27" t="s">
+      <c r="D34" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="29"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="26"/>
     </row>
     <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
@@ -3623,13 +3623,13 @@
       <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D39" s="27" t="s">
+      <c r="D39" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="29"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="26"/>
     </row>
     <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
@@ -3665,13 +3665,13 @@
       <c r="C42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D42" s="27" t="s">
+      <c r="D42" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="29"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="26"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
@@ -3689,13 +3689,13 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="43" t="s">
+      <c r="D44" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="45"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="38"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
@@ -3713,25 +3713,25 @@
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-      <c r="D46" s="43" t="s">
+      <c r="D46" s="36" t="s">
         <v>378</v>
       </c>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="45"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="38"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="43" t="s">
+      <c r="D47" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="45"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="38"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
@@ -3743,13 +3743,13 @@
       <c r="C48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D48" s="27" t="s">
+      <c r="D48" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="29"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="26"/>
     </row>
     <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
@@ -3797,13 +3797,13 @@
       <c r="C52" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D52" s="27" t="s">
+      <c r="D52" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="29"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="26"/>
     </row>
     <row r="53" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
@@ -3863,25 +3863,25 @@
       <c r="C57" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="27" t="s">
+      <c r="D57" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="29"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="26"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
-      <c r="D58" s="30" t="s">
+      <c r="D58" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="E58" s="31"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="32"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="44"/>
     </row>
     <row r="59" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2"/>
@@ -3929,13 +3929,13 @@
       <c r="C62" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D62" s="27" t="s">
+      <c r="D62" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="E62" s="28"/>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="29"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="26"/>
     </row>
     <row r="63" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2"/>
@@ -4067,13 +4067,13 @@
       <c r="C73" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D73" s="27" t="s">
+      <c r="D73" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="E73" s="28"/>
-      <c r="F73" s="28"/>
-      <c r="G73" s="28"/>
-      <c r="H73" s="29"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="26"/>
     </row>
     <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="2"/>
@@ -4145,13 +4145,13 @@
       <c r="C79" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D79" s="27" t="s">
+      <c r="D79" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="E79" s="28"/>
-      <c r="F79" s="28"/>
-      <c r="G79" s="28"/>
-      <c r="H79" s="29"/>
+      <c r="E79" s="25"/>
+      <c r="F79" s="25"/>
+      <c r="G79" s="25"/>
+      <c r="H79" s="26"/>
     </row>
     <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="2"/>
@@ -4169,25 +4169,25 @@
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
-      <c r="D81" s="36" t="s">
+      <c r="D81" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="E81" s="37"/>
-      <c r="F81" s="37"/>
-      <c r="G81" s="37"/>
-      <c r="H81" s="38"/>
+      <c r="E81" s="28"/>
+      <c r="F81" s="28"/>
+      <c r="G81" s="28"/>
+      <c r="H81" s="29"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
-      <c r="D82" s="39" t="s">
+      <c r="D82" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="E82" s="40"/>
-      <c r="F82" s="40"/>
-      <c r="G82" s="40"/>
-      <c r="H82" s="41"/>
+      <c r="E82" s="31"/>
+      <c r="F82" s="31"/>
+      <c r="G82" s="31"/>
+      <c r="H82" s="32"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="2"/>
@@ -4217,13 +4217,13 @@
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
-      <c r="D85" s="36" t="s">
+      <c r="D85" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="E85" s="37"/>
-      <c r="F85" s="37"/>
-      <c r="G85" s="37"/>
-      <c r="H85" s="38"/>
+      <c r="E85" s="28"/>
+      <c r="F85" s="28"/>
+      <c r="G85" s="28"/>
+      <c r="H85" s="29"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
@@ -4235,13 +4235,13 @@
       <c r="C86" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D86" s="27" t="s">
+      <c r="D86" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="E86" s="28"/>
-      <c r="F86" s="28"/>
-      <c r="G86" s="28"/>
-      <c r="H86" s="29"/>
+      <c r="E86" s="25"/>
+      <c r="F86" s="25"/>
+      <c r="G86" s="25"/>
+      <c r="H86" s="26"/>
     </row>
     <row r="87" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87" s="2"/>
@@ -4305,24 +4305,61 @@
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D87:H87"/>
+    <mergeCell ref="D88:H88"/>
+    <mergeCell ref="D89:H89"/>
+    <mergeCell ref="D74:H74"/>
+    <mergeCell ref="D63:H63"/>
+    <mergeCell ref="D64:H64"/>
+    <mergeCell ref="D65:H65"/>
+    <mergeCell ref="D66:H66"/>
+    <mergeCell ref="D67:H67"/>
+    <mergeCell ref="D68:H68"/>
+    <mergeCell ref="D69:H69"/>
+    <mergeCell ref="D70:H70"/>
+    <mergeCell ref="D71:H71"/>
+    <mergeCell ref="D72:H72"/>
+    <mergeCell ref="D90:H90"/>
+    <mergeCell ref="D91:H91"/>
+    <mergeCell ref="D86:H86"/>
+    <mergeCell ref="D75:H75"/>
+    <mergeCell ref="D76:H76"/>
+    <mergeCell ref="D77:H77"/>
+    <mergeCell ref="D78:H78"/>
+    <mergeCell ref="D79:H79"/>
+    <mergeCell ref="D80:H80"/>
+    <mergeCell ref="D81:H81"/>
+    <mergeCell ref="D82:H82"/>
+    <mergeCell ref="D83:H83"/>
+    <mergeCell ref="D84:H84"/>
+    <mergeCell ref="D85:H85"/>
+    <mergeCell ref="D73:H73"/>
+    <mergeCell ref="D62:H62"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D56:H56"/>
+    <mergeCell ref="D57:H57"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="D61:H61"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D49:H49"/>
     <mergeCell ref="D37:H37"/>
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="D21:H21"/>
@@ -4339,61 +4376,24 @@
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="D26:H26"/>
     <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D73:H73"/>
-    <mergeCell ref="D62:H62"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D56:H56"/>
-    <mergeCell ref="D57:H57"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="D61:H61"/>
-    <mergeCell ref="D90:H90"/>
-    <mergeCell ref="D91:H91"/>
-    <mergeCell ref="D86:H86"/>
-    <mergeCell ref="D75:H75"/>
-    <mergeCell ref="D76:H76"/>
-    <mergeCell ref="D77:H77"/>
-    <mergeCell ref="D78:H78"/>
-    <mergeCell ref="D79:H79"/>
-    <mergeCell ref="D80:H80"/>
-    <mergeCell ref="D81:H81"/>
-    <mergeCell ref="D82:H82"/>
-    <mergeCell ref="D83:H83"/>
-    <mergeCell ref="D84:H84"/>
-    <mergeCell ref="D85:H85"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D87:H87"/>
-    <mergeCell ref="D88:H88"/>
-    <mergeCell ref="D89:H89"/>
-    <mergeCell ref="D74:H74"/>
-    <mergeCell ref="D63:H63"/>
-    <mergeCell ref="D64:H64"/>
-    <mergeCell ref="D65:H65"/>
-    <mergeCell ref="D66:H66"/>
-    <mergeCell ref="D67:H67"/>
-    <mergeCell ref="D68:H68"/>
-    <mergeCell ref="D69:H69"/>
-    <mergeCell ref="D70:H70"/>
-    <mergeCell ref="D71:H71"/>
-    <mergeCell ref="D72:H72"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4423,25 +4423,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -4495,13 +4495,13 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="45"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -4513,13 +4513,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -4537,25 +4537,25 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="38"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="41"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
@@ -4603,13 +4603,13 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
     </row>
     <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
@@ -4681,25 +4681,25 @@
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="26"/>
     </row>
     <row r="22" spans="1:8" ht="57" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="42" t="s">
         <v>387</v>
       </c>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="32"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="44"/>
     </row>
     <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
@@ -4735,13 +4735,13 @@
       <c r="C25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="D25" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="29"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="26"/>
     </row>
     <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
@@ -4789,13 +4789,13 @@
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="27" t="s">
+      <c r="D29" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="26"/>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
@@ -4855,13 +4855,13 @@
       <c r="C34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="27" t="s">
+      <c r="D34" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="29"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="26"/>
     </row>
     <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
@@ -4897,13 +4897,13 @@
       <c r="C37" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="27" t="s">
+      <c r="D37" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="29"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="26"/>
     </row>
     <row r="38" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
@@ -4967,12 +4967,28 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
@@ -4985,28 +5001,12 @@
     <mergeCell ref="D17:H17"/>
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5027,13 +5027,13 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
@@ -5051,25 +5051,25 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="38"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="29"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="41"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="32"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
@@ -5117,13 +5117,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="24" t="s">
         <v>280</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -5159,13 +5159,13 @@
       <c r="C11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="24" t="s">
         <v>281</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="29"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="26"/>
     </row>
     <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
@@ -5201,13 +5201,13 @@
       <c r="C14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="29"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="26"/>
     </row>
     <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
@@ -5283,6 +5283,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
     <mergeCell ref="D12:H12"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="D2:H2"/>
@@ -5295,14 +5303,6 @@
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5332,25 +5332,25 @@
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="29"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="26"/>
     </row>
     <row r="8" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -5404,13 +5404,13 @@
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="43" t="s">
+      <c r="D13" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="45"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="38"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
@@ -5434,13 +5434,13 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
     </row>
     <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
@@ -5458,25 +5458,25 @@
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="38"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="41"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="32"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
@@ -5524,13 +5524,13 @@
       <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="29"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26"/>
     </row>
     <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
@@ -5548,25 +5548,25 @@
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="36" t="s">
+      <c r="D24" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="38"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="29"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="39" t="s">
+      <c r="D25" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="40"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="41"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="32"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
@@ -5602,13 +5602,13 @@
       <c r="C28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="29"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="26"/>
     </row>
     <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
@@ -5626,25 +5626,25 @@
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
-      <c r="D30" s="36" t="s">
+      <c r="D30" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="38"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="29"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="39" t="s">
+      <c r="D31" s="30" t="s">
         <v>189</v>
       </c>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="41"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="32"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
@@ -5668,13 +5668,13 @@
       <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="29"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="26"/>
     </row>
     <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
@@ -5746,25 +5746,25 @@
       <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D39" s="27" t="s">
+      <c r="D39" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="29"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="26"/>
     </row>
     <row r="40" spans="1:8" ht="78.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="30" t="s">
+      <c r="D40" s="42" t="s">
         <v>308</v>
       </c>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="32"/>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="44"/>
     </row>
     <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
@@ -5800,13 +5800,13 @@
       <c r="C43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="29"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="26"/>
     </row>
     <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
@@ -5866,25 +5866,25 @@
       <c r="C48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D48" s="27" t="s">
+      <c r="D48" s="24" t="s">
         <v>252</v>
       </c>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="29"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="26"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
-      <c r="D49" s="24" t="s">
+      <c r="D49" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
-      <c r="H49" s="26"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="41"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
@@ -5902,25 +5902,25 @@
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="24" t="s">
+      <c r="D51" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="E51" s="25"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="25"/>
-      <c r="H51" s="26"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="41"/>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="24" t="s">
+      <c r="D52" s="39" t="s">
         <v>311</v>
       </c>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="26"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="41"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
@@ -5932,13 +5932,13 @@
       <c r="C53" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D53" s="27" t="s">
+      <c r="D53" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="29"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="26"/>
     </row>
     <row r="54" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
@@ -5974,13 +5974,13 @@
       <c r="C56" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D56" s="27" t="s">
+      <c r="D56" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="E56" s="28"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="29"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="26"/>
     </row>
     <row r="57" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2"/>
@@ -6044,12 +6044,36 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="D61:H61"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D58:H58"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D56:H56"/>
+    <mergeCell ref="D57:H57"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
     <mergeCell ref="D21:H21"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D34:H34"/>
@@ -6066,36 +6090,12 @@
     <mergeCell ref="D30:H30"/>
     <mergeCell ref="D31:H31"/>
     <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="D61:H61"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="D58:H58"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D56:H56"/>
-    <mergeCell ref="D57:H57"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6130,25 +6130,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -6166,49 +6166,49 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="45"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="36" t="s">
         <v>313</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="45"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="45"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="38"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="45"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -6220,13 +6220,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -6244,25 +6244,25 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="38"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="41"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
@@ -6310,13 +6310,13 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
     </row>
     <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
@@ -6376,25 +6376,25 @@
       <c r="C20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="26"/>
     </row>
     <row r="21" spans="1:8" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="26"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="41"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -6406,13 +6406,13 @@
       <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="29"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26"/>
     </row>
     <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
@@ -6460,13 +6460,13 @@
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="24" t="s">
         <v>264</v>
       </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="26"/>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
@@ -6502,13 +6502,13 @@
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="27" t="s">
+      <c r="D29" s="24" t="s">
         <v>267</v>
       </c>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="26"/>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
@@ -6572,6 +6572,27 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="D2:H2"/>
@@ -6584,27 +6605,6 @@
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="D11:H11"/>
     <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
   </mergeCells>
   <pageMargins left="0.70866141732283461" right="0.70866141732283461" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6635,25 +6635,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -6707,13 +6707,13 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="45"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
@@ -6737,13 +6737,13 @@
       <c r="C9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="29"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
@@ -6761,25 +6761,25 @@
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="36" t="s">
+      <c r="D11" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="38"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="29"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="41"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="32"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
@@ -6827,13 +6827,13 @@
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="26"/>
     </row>
     <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
@@ -6905,25 +6905,25 @@
       <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="29"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26"/>
     </row>
     <row r="23" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="42" t="s">
         <v>297</v>
       </c>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="32"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="44"/>
     </row>
     <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
@@ -6959,13 +6959,13 @@
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="26"/>
     </row>
     <row r="27" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
@@ -7013,25 +7013,25 @@
       <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="29"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="26"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="26"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="41"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
@@ -7049,25 +7049,25 @@
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="26"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="41"/>
     </row>
     <row r="34" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="26"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="41"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
@@ -7079,13 +7079,13 @@
       <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="27" t="s">
+      <c r="D35" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="29"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="26"/>
     </row>
     <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
@@ -7121,13 +7121,13 @@
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="29"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="26"/>
     </row>
     <row r="39" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
@@ -7191,12 +7191,28 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
     <mergeCell ref="D21:H21"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="D11:H11"/>
@@ -7209,28 +7225,12 @@
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7261,25 +7261,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -7333,13 +7333,13 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="45"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -7351,13 +7351,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -7375,25 +7375,25 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="38"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="41"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
@@ -7441,13 +7441,13 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
@@ -7519,73 +7519,73 @@
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="26"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="42" t="s">
         <v>272</v>
       </c>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="32"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="44"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="30" t="s">
+      <c r="D23" s="42" t="s">
         <v>326</v>
       </c>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="32"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="44"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="42" t="s">
         <v>327</v>
       </c>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="32"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="44"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-      <c r="D25" s="30" t="s">
+      <c r="D25" s="42" t="s">
         <v>328</v>
       </c>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="32"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="44"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="42" t="s">
         <v>329</v>
       </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="32"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="44"/>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
@@ -7621,13 +7621,13 @@
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="27" t="s">
+      <c r="D29" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="26"/>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
@@ -7675,25 +7675,25 @@
       <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="29"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="26"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="26"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="41"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
@@ -7711,25 +7711,25 @@
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
-      <c r="D36" s="24" t="s">
+      <c r="D36" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="26"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="41"/>
     </row>
     <row r="37" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="24" t="s">
+      <c r="D37" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="26"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="41"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
@@ -7741,13 +7741,13 @@
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="29"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="26"/>
     </row>
     <row r="39" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
@@ -7783,13 +7783,13 @@
       <c r="C41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D41" s="27" t="s">
+      <c r="D41" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="29"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="26"/>
     </row>
     <row r="42" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
@@ -7853,34 +7853,6 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
     <mergeCell ref="D35:H35"/>
     <mergeCell ref="D36:H36"/>
     <mergeCell ref="D21:H21"/>
@@ -7897,6 +7869,34 @@
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7927,25 +7927,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -7999,13 +7999,13 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="45"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -8017,13 +8017,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -8041,25 +8041,25 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="38"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="41"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
@@ -8107,13 +8107,13 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
     </row>
     <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
@@ -8131,25 +8131,25 @@
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="38"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="29"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="41"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="32"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
@@ -8197,13 +8197,13 @@
       <c r="C22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="24" t="s">
         <v>273</v>
       </c>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="29"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="26"/>
     </row>
     <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
@@ -8275,25 +8275,25 @@
       <c r="C28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="29"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="26"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
-      <c r="D29" s="30" t="s">
+      <c r="D29" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="32"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="44"/>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
@@ -8323,13 +8323,13 @@
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="49" t="s">
+      <c r="D32" s="46" t="s">
         <v>337</v>
       </c>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="51"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="48"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
@@ -8349,25 +8349,25 @@
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="52" t="s">
+      <c r="D34" s="49" t="s">
         <v>338</v>
       </c>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="54"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="51"/>
     </row>
     <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="55" t="s">
+      <c r="D35" s="52" t="s">
         <v>340</v>
       </c>
-      <c r="E35" s="56"/>
-      <c r="F35" s="56"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="57"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="54"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
@@ -8379,25 +8379,25 @@
       <c r="C36" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="27" t="s">
+      <c r="D36" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="29"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="26"/>
     </row>
     <row r="37" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="24" t="s">
+      <c r="D37" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="26"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="41"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
@@ -8445,25 +8445,25 @@
       <c r="C41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D41" s="27" t="s">
+      <c r="D41" s="24" t="s">
         <v>237</v>
       </c>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="29"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="26"/>
     </row>
     <row r="42" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="39" t="s">
         <v>274</v>
       </c>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="26"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="41"/>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
@@ -8481,25 +8481,25 @@
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-      <c r="D44" s="24" t="s">
+      <c r="D44" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="26"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="41"/>
     </row>
     <row r="45" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
-      <c r="D45" s="24" t="s">
+      <c r="D45" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="26"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="41"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -8511,37 +8511,37 @@
       <c r="C46" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D46" s="27" t="s">
+      <c r="D46" s="24" t="s">
         <v>277</v>
       </c>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="29"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="26"/>
     </row>
     <row r="47" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-      <c r="D47" s="24" t="s">
+      <c r="D47" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="26"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="41"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
-      <c r="D48" s="24" t="s">
+      <c r="D48" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="26"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="41"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
@@ -8553,61 +8553,61 @@
       <c r="C49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D49" s="46" t="s">
+      <c r="D49" s="55" t="s">
         <v>278</v>
       </c>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="48"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="57"/>
     </row>
     <row r="50" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-      <c r="D50" s="24" t="s">
+      <c r="D50" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
-      <c r="H50" s="26"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="41"/>
     </row>
     <row r="51" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-      <c r="D51" s="24" t="s">
+      <c r="D51" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E51" s="25"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="25"/>
-      <c r="H51" s="26"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="41"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-      <c r="D52" s="24" t="s">
+      <c r="D52" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="26"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="41"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
-      <c r="D53" s="24" t="s">
+      <c r="D53" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="25"/>
-      <c r="H53" s="26"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="41"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
@@ -8623,6 +8623,39 @@
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
     <mergeCell ref="D27:H27"/>
     <mergeCell ref="D26:H26"/>
     <mergeCell ref="D8:H8"/>
@@ -8639,39 +8672,6 @@
     <mergeCell ref="D14:H14"/>
     <mergeCell ref="D22:H22"/>
     <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D51:H51"/>
-    <mergeCell ref="D49:H49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8702,25 +8702,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -8774,13 +8774,13 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="45"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -8792,13 +8792,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -8816,25 +8816,25 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="38"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="41"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
@@ -8882,13 +8882,13 @@
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
     </row>
     <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
@@ -8960,25 +8960,25 @@
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="26"/>
     </row>
     <row r="22" spans="1:8" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="42" t="s">
         <v>349</v>
       </c>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="32"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="44"/>
     </row>
     <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
@@ -9014,13 +9014,13 @@
       <c r="C25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="D25" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="29"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="26"/>
     </row>
     <row r="26" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
@@ -9080,13 +9080,13 @@
       <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="29"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="26"/>
     </row>
     <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
@@ -9146,13 +9146,13 @@
       <c r="C35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="27" t="s">
+      <c r="D35" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="29"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="26"/>
     </row>
     <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
@@ -9188,13 +9188,13 @@
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="29"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="26"/>
     </row>
     <row r="39" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
@@ -9258,24 +9258,15 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
     <mergeCell ref="D34:H34"/>
     <mergeCell ref="D21:H21"/>
     <mergeCell ref="D22:H22"/>
@@ -9290,15 +9281,24 @@
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="D27:H27"/>
     <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9327,25 +9327,25 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -9399,13 +9399,13 @@
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="45"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -9417,13 +9417,13 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="29"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="26"/>
     </row>
     <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
@@ -9441,25 +9441,25 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="38"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="29"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="41"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
@@ -9519,13 +9519,13 @@
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="26"/>
     </row>
     <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
@@ -9543,25 +9543,25 @@
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="38"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="32"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
@@ -9621,13 +9621,13 @@
       <c r="C24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="29"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="26"/>
     </row>
     <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
@@ -9645,25 +9645,25 @@
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="36" t="s">
+      <c r="D26" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="38"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="29"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="39" t="s">
+      <c r="D27" s="30" t="s">
         <v>189</v>
       </c>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="41"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="32"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
@@ -9711,13 +9711,13 @@
       <c r="C31" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="29"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="26"/>
     </row>
     <row r="32" spans="1:8" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
@@ -9777,13 +9777,13 @@
       <c r="C36" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="27" t="s">
+      <c r="D36" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="29"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="26"/>
     </row>
     <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
@@ -9813,25 +9813,25 @@
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="24" t="s">
+      <c r="D39" s="39" t="s">
         <v>356</v>
       </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="26"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="41"/>
     </row>
     <row r="40" spans="1:8" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="24" t="s">
+      <c r="D40" s="39" t="s">
         <v>357</v>
       </c>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="26"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="41"/>
     </row>
     <row r="41" spans="1:8" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
@@ -9855,13 +9855,13 @@
       <c r="C42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D42" s="27" t="s">
+      <c r="D42" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="29"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="26"/>
     </row>
     <row r="43" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
@@ -9933,13 +9933,13 @@
       <c r="C48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D48" s="27" t="s">
+      <c r="D48" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="29"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="26"/>
     </row>
     <row r="49" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
@@ -10008,25 +10008,22 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D36:H36"/>
     <mergeCell ref="D31:H31"/>
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="D52:H52"/>
@@ -10043,22 +10040,25 @@
     <mergeCell ref="D45:H45"/>
     <mergeCell ref="D46:H46"/>
     <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10086,13 +10086,13 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
@@ -10122,13 +10122,13 @@
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="45"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -10140,13 +10140,13 @@
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="29"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
@@ -10278,13 +10278,13 @@
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="26"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
@@ -10302,25 +10302,25 @@
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="38"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="29"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
-      <c r="D19" s="39" t="s">
+      <c r="D19" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="32"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="12"/>
@@ -10368,25 +10368,25 @@
       <c r="C23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="29"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="26"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="32"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="44"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="12"/>
@@ -10446,13 +10446,13 @@
       <c r="C29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="27" t="s">
+      <c r="D29" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="26"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="12"/>
@@ -10512,13 +10512,13 @@
       <c r="C34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D34" s="27" t="s">
+      <c r="D34" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="29"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="26"/>
     </row>
     <row r="35" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12"/>
@@ -10578,13 +10578,13 @@
       <c r="C39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D39" s="27" t="s">
+      <c r="D39" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="29"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="26"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="12"/>
@@ -10716,13 +10716,13 @@
       <c r="C50" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D50" s="27" t="s">
+      <c r="D50" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="E50" s="28"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="29"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="26"/>
     </row>
     <row r="51" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12"/>
@@ -10786,12 +10786,40 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D52:H52"/>
+    <mergeCell ref="D53:H53"/>
+    <mergeCell ref="D54:H54"/>
+    <mergeCell ref="D55:H55"/>
+    <mergeCell ref="D46:H46"/>
+    <mergeCell ref="D47:H47"/>
+    <mergeCell ref="D48:H48"/>
+    <mergeCell ref="D49:H49"/>
+    <mergeCell ref="D50:H50"/>
+    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D45:H45"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D35:H35"/>
+    <mergeCell ref="D36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="D39:H39"/>
+    <mergeCell ref="D40:H40"/>
+    <mergeCell ref="D41:H41"/>
+    <mergeCell ref="D42:H42"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D33:H33"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D29:H29"/>
+    <mergeCell ref="D30:H30"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D32:H32"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
@@ -10804,40 +10832,12 @@
     <mergeCell ref="D16:H16"/>
     <mergeCell ref="D17:H17"/>
     <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D33:H33"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D29:H29"/>
-    <mergeCell ref="D30:H30"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D32:H32"/>
-    <mergeCell ref="D45:H45"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D35:H35"/>
-    <mergeCell ref="D36:H36"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="D39:H39"/>
-    <mergeCell ref="D40:H40"/>
-    <mergeCell ref="D41:H41"/>
-    <mergeCell ref="D42:H42"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="D44:H44"/>
-    <mergeCell ref="D52:H52"/>
-    <mergeCell ref="D53:H53"/>
-    <mergeCell ref="D54:H54"/>
-    <mergeCell ref="D55:H55"/>
-    <mergeCell ref="D46:H46"/>
-    <mergeCell ref="D47:H47"/>
-    <mergeCell ref="D48:H48"/>
-    <mergeCell ref="D49:H49"/>
-    <mergeCell ref="D50:H50"/>
-    <mergeCell ref="D51:H51"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
